--- a/AAII_Financials/Quarterly/IPSC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IPSC_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="92">
   <si>
     <t>IPSC</t>
   </si>
@@ -656,121 +656,124 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E8" s="3">
         <v>100</v>
       </c>
       <c r="F8" s="3">
+        <v>100</v>
+      </c>
+      <c r="G8" s="3">
         <v>1700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1100</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
@@ -783,8 +786,8 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
+      <c r="P8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q8" s="3">
         <v>0</v>
@@ -798,8 +801,11 @@
       <c r="T8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -854,8 +860,11 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -910,8 +919,11 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -932,64 +944,68 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>22300</v>
+      </c>
+      <c r="E12" s="3">
         <v>22800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>22700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>24900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>25600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>25900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>24500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>21200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>21800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>19500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>18900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>15400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>39700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>10800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>8500</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1044,20 +1060,23 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E14" s="3">
         <v>4000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>4200</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
@@ -1068,40 +1087,43 @@
         <v>0</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>10000</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
         <v>4700</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>4700</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1156,8 +1178,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1175,91 +1200,95 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>44000</v>
+      </c>
+      <c r="E17" s="3">
         <v>35800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>35200</v>
-      </c>
-      <c r="F17" s="3">
-        <v>33800</v>
       </c>
       <c r="G17" s="3">
         <v>33800</v>
       </c>
       <c r="H17" s="3">
+        <v>33800</v>
+      </c>
+      <c r="I17" s="3">
         <v>34000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>32700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>38500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>28000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>25800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>23000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>18100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>53900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>13100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>15500</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-43700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-35700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-35100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-32100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-33300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-31800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-31300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-37400</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1272,23 +1301,26 @@
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P18" s="3">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-13100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-15500</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1309,8 +1341,9 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1318,26 +1351,26 @@
         <v>3500</v>
       </c>
       <c r="E20" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F20" s="3">
         <v>2900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1350,50 +1383,53 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>200</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-36700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-28800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-29000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-26700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-28400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-27600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-29000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-36000</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1406,23 +1442,26 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-12600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-15000</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1430,10 +1469,10 @@
         <v>0</v>
       </c>
       <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
         <v>100</v>
-      </c>
-      <c r="F22" s="3">
-        <v>400</v>
       </c>
       <c r="G22" s="3">
         <v>400</v>
@@ -1442,7 +1481,7 @@
         <v>400</v>
       </c>
       <c r="I22" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="J22" s="3">
         <v>300</v>
@@ -1460,16 +1499,16 @@
         <v>300</v>
       </c>
       <c r="O22" s="3">
+        <v>300</v>
+      </c>
+      <c r="P22" s="3">
         <v>400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>100</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
+      <c r="R22" s="3">
+        <v>0</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>3</v>
@@ -1477,79 +1516,85 @@
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-40300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-32100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-32300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-30100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-31700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-30700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-31000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-37500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-28200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-26000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-23300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-18300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-53600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-13100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-15300</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E24" s="3">
         <v>600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1200</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
         <v>0</v>
       </c>
@@ -1562,8 +1607,8 @@
       <c r="K24" s="3">
         <v>0</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
+      <c r="L24" s="3">
+        <v>0</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
@@ -1580,8 +1625,8 @@
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
+      <c r="R24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S24" s="3">
         <v>0</v>
@@ -1589,8 +1634,11 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1645,120 +1693,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-39400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-32700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-33300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-31300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-31700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-30700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-31000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-37500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-28200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-26000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-23300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-18300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-53600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-13100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-15300</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-39400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-32700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-33300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-31300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-31700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-30700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-31000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-37500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-28200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-26000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-23300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-18300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-53600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-13100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-15300</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1813,8 +1870,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1869,8 +1929,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1925,8 +1988,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1981,8 +2047,11 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1990,26 +2059,26 @@
         <v>-3500</v>
       </c>
       <c r="E32" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="F32" s="3">
         <v>-2900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2022,79 +2091,85 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-200</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-39400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-32700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-33300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-31300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-31700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-30700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-31000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-37500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-28200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-26000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-23300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-18300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-53600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-13100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-15300</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2149,125 +2224,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-39400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-32700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-33300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-31300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-31700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-30700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-31000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-37500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-28200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-26000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-23300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-18300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-53600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-13100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-15300</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2288,8 +2372,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2310,47 +2395,48 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>47300</v>
+      </c>
+      <c r="E41" s="3">
         <v>55300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>64400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>86800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>84300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>111400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>112800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>126000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>56400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>101300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>272300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>79500</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2366,47 +2452,50 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>125400</v>
+      </c>
+      <c r="E42" s="3">
         <v>114200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>92000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>164600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>231200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>244500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>266000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>235000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>166400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>193900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>125300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>103500</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2422,8 +2511,11 @@
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2478,8 +2570,11 @@
       <c r="T43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2534,47 +2629,50 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E45" s="3">
         <v>4200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2400</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2590,47 +2688,50 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>177000</v>
+      </c>
+      <c r="E46" s="3">
         <v>173700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>161300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>255900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>319700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>361600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>383800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>365300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>228200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>300400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>402600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>185300</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2646,47 +2747,50 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>89100</v>
+      </c>
+      <c r="E47" s="3">
         <v>114800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>144600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>83300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>51900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>39400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>50600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>105400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>135900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>105200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>42500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>63100</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2702,47 +2806,50 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>92100</v>
+      </c>
+      <c r="E48" s="3">
         <v>106500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>108800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>114000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>111700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>107400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>94700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>76400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>69800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>60700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>46700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>33100</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2758,8 +2865,11 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2814,8 +2924,11 @@
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2870,8 +2983,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2926,8 +3042,11 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2938,35 +3057,35 @@
         <v>2500</v>
       </c>
       <c r="F52" s="3">
+        <v>2500</v>
+      </c>
+      <c r="G52" s="3">
         <v>2900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3300</v>
-      </c>
-      <c r="K52" s="3">
-        <v>3500</v>
       </c>
       <c r="L52" s="3">
         <v>3500</v>
       </c>
       <c r="M52" s="3">
+        <v>3500</v>
+      </c>
+      <c r="N52" s="3">
         <v>3800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4500</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2982,8 +3101,11 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3038,47 +3160,50 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>360700</v>
+      </c>
+      <c r="E54" s="3">
         <v>397600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>417200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>456200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>486500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>511800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>532600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>550300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>437400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>469700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>495600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>286100</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3094,8 +3219,11 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3116,8 +3244,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3138,47 +3267,48 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E57" s="3">
         <v>5900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>9900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>11600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>13400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8800</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3194,8 +3324,11 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3206,26 +3339,26 @@
         <v>0</v>
       </c>
       <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
         <v>10300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1600</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K58" s="3">
+      <c r="K58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L58" s="3">
         <v>1000</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3241,8 +3374,8 @@
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
+      <c r="R58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S58" s="3">
         <v>0</v>
@@ -3250,47 +3383,50 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E59" s="3">
         <v>14500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>15500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>13900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>17900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>17200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>15900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>12100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>8200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4100</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3306,47 +3442,50 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E60" s="3">
         <v>20400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>19200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>27700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>29800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>26900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>21600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>22000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>15700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>19900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>21200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>12900</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3362,8 +3501,11 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3377,32 +3519,32 @@
         <v>0</v>
       </c>
       <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>3700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>10000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>9900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>9800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>9700</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3418,47 +3560,50 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>158100</v>
+      </c>
+      <c r="E62" s="3">
         <v>157900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>150400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>151400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>150300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>148500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>144600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>131700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>16600</v>
-      </c>
-      <c r="L62" s="3">
-        <v>17000</v>
       </c>
       <c r="M62" s="3">
         <v>17000</v>
       </c>
       <c r="N62" s="3">
+        <v>17000</v>
+      </c>
+      <c r="O62" s="3">
         <v>15600</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3474,8 +3619,11 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3530,8 +3678,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3586,8 +3737,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3642,47 +3796,50 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>175900</v>
+      </c>
+      <c r="E66" s="3">
         <v>178300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>169600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>179100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>183800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>181500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>174600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>163600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>41100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>46700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>48000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>38200</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3698,8 +3855,11 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3720,8 +3880,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3776,8 +3937,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3832,8 +3996,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3868,11 +4035,11 @@
         <v>0</v>
       </c>
       <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
         <v>339400</v>
       </c>
-      <c r="O70" s="3">
-        <v>0</v>
-      </c>
       <c r="P70" s="3">
         <v>0</v>
       </c>
@@ -3888,8 +4055,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3944,47 +4114,50 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-655800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-616400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-583700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-550400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-519100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-487400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-456700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-425700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-388200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-360000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-334000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-310700</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4000,8 +4173,11 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4056,8 +4232,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4112,8 +4291,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4168,47 +4350,50 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>184800</v>
+      </c>
+      <c r="E76" s="3">
         <v>219200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>247600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>277200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>302700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>330200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>358000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>386700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>396200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>423000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>447600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-91600</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4224,8 +4409,11 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4280,125 +4468,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-39400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-32700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-33300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-31300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-31700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-30700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-31000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-37500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-28200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-26000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-23300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-18300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-53600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-13100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-15300</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4419,64 +4616,68 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E83" s="3">
         <v>3400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2900</v>
-      </c>
-      <c r="G83" s="3">
-        <v>2800</v>
       </c>
       <c r="H83" s="3">
         <v>2800</v>
       </c>
       <c r="I83" s="3">
+        <v>2800</v>
+      </c>
+      <c r="J83" s="3">
         <v>1700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>300</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4531,8 +4732,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4587,8 +4791,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4643,8 +4850,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4699,8 +4909,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4755,64 +4968,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-26200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-13600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-19300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-29200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-22900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-24200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-25600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>86800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-24400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-24000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-18500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-22200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-41300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-9200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-11900</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4833,64 +5052,68 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-6300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-9800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-10500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-16700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-15700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-10600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-700</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4945,8 +5168,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5001,64 +5227,70 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E94" s="3">
         <v>4200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>7000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>31300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>22700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>12500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-44000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-20600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-147100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-11600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-119000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-22800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>1700</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5079,8 +5311,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5135,8 +5368,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5191,8 +5427,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5247,8 +5486,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5303,55 +5545,58 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E100" s="3">
         <v>300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-10100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>400</v>
-      </c>
-      <c r="G100" s="3">
-        <v>100</v>
       </c>
       <c r="H100" s="3">
         <v>100</v>
       </c>
       <c r="I100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>26900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>224600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>193500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>47700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>9600</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
+      <c r="R100" s="3">
+        <v>0</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
@@ -5359,8 +5604,11 @@
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5415,60 +5663,66 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-9100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-22400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-27100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-13000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>69600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-44800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-171500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>194500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>52300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-16300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-10200</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IPSC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IPSC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="92">
   <si>
     <t>IPSC</t>
   </si>
@@ -656,127 +656,131 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>900</v>
+      </c>
+      <c r="E8" s="3">
         <v>300</v>
-      </c>
-      <c r="E8" s="3">
-        <v>100</v>
       </c>
       <c r="F8" s="3">
         <v>100</v>
       </c>
       <c r="G8" s="3">
+        <v>100</v>
+      </c>
+      <c r="H8" s="3">
         <v>1700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1100</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
@@ -789,8 +793,8 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3">
-        <v>0</v>
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R8" s="3">
         <v>0</v>
@@ -804,8 +808,11 @@
       <c r="U8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -863,8 +870,11 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -922,8 +932,11 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -945,67 +958,71 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>23400</v>
+      </c>
+      <c r="E12" s="3">
         <v>22300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>22800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>22700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>24900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>25600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>25900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>24500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>21200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>21800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>19500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>18900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>15400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>39700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>10800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>8500</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1063,23 +1080,26 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>13100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>4000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>4200</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
         <v>0</v>
       </c>
@@ -1090,40 +1110,43 @@
         <v>0</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>10000</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
         <v>4700</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>4700</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1181,8 +1204,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1201,97 +1227,101 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>32200</v>
+      </c>
+      <c r="E17" s="3">
         <v>44000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>35800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>35200</v>
-      </c>
-      <c r="G17" s="3">
-        <v>33800</v>
       </c>
       <c r="H17" s="3">
         <v>33800</v>
       </c>
       <c r="I17" s="3">
+        <v>33800</v>
+      </c>
+      <c r="J17" s="3">
         <v>34000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>32700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>38500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>28000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>25800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>23000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>18100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>53900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>13100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>15500</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-31300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-43700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-35700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-35100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-32100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-33300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-31800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-31300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-37400</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1304,23 +1334,26 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3">
         <v>-13100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-15500</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1342,38 +1375,39 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>3500</v>
+        <v>3200</v>
       </c>
       <c r="E20" s="3">
         <v>3500</v>
       </c>
       <c r="F20" s="3">
+        <v>3500</v>
+      </c>
+      <c r="G20" s="3">
         <v>2900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1386,53 +1420,56 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-24800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-36700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-28800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-29000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-26700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-28400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-27600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-29000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-36000</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1445,23 +1482,26 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3">
         <v>-12600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-15000</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1472,10 +1512,10 @@
         <v>0</v>
       </c>
       <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
         <v>100</v>
-      </c>
-      <c r="G22" s="3">
-        <v>400</v>
       </c>
       <c r="H22" s="3">
         <v>400</v>
@@ -1484,7 +1524,7 @@
         <v>400</v>
       </c>
       <c r="J22" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="K22" s="3">
         <v>300</v>
@@ -1502,16 +1542,16 @@
         <v>300</v>
       </c>
       <c r="P22" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q22" s="3">
         <v>400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>100</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
+      <c r="S22" s="3">
+        <v>0</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
@@ -1519,85 +1559,91 @@
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-28100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-40300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-32100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-32300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-30100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-31700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-30700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-31000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-37500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-28200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-26000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-23300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-18300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-53600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-13100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-15300</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>-900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1200</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
         <v>0</v>
       </c>
@@ -1610,8 +1656,8 @@
       <c r="L24" s="3">
         <v>0</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
+      <c r="M24" s="3">
+        <v>0</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
@@ -1628,8 +1674,8 @@
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
+      <c r="S24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T24" s="3">
         <v>0</v>
@@ -1637,8 +1683,11 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1696,126 +1745,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-28100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-39400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-32700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-33300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-31300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-31700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-30700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-31000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-37500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-28200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-26000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-23300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-18300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-53600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-13100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-15300</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-28100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-39400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-32700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-33300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-31300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-31700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-30700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-31000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-37500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-28200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-26000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-23300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-18300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-53600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-13100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-15300</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1873,8 +1931,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1932,8 +1993,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1991,8 +2055,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2050,38 +2117,41 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-3500</v>
+        <v>-3200</v>
       </c>
       <c r="E32" s="3">
         <v>-3500</v>
       </c>
       <c r="F32" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="G32" s="3">
         <v>-2900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2094,82 +2164,88 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-28100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-39400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-32700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-33300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-31300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-31700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-30700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-31000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-37500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-28200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-26000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-23300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-18300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-53600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-13100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-15300</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2227,131 +2303,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-28100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-39400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-32700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-33300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-31300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-31700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-30700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-31000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-37500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-28200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-26000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-23300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-18300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-53600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-13100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-15300</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2373,8 +2458,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2396,50 +2482,51 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>46800</v>
+      </c>
+      <c r="E41" s="3">
         <v>47300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>55300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>64400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>86800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>84300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>111400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>112800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>126000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>56400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>101300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>272300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>79500</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2455,50 +2542,53 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>145200</v>
+      </c>
+      <c r="E42" s="3">
         <v>125400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>114200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>92000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>164600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>231200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>244500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>266000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>235000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>166400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>193900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>125300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>103500</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2514,8 +2604,11 @@
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2573,8 +2666,11 @@
       <c r="U43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2632,50 +2728,53 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E45" s="3">
         <v>4300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2400</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2691,50 +2790,53 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>199800</v>
+      </c>
+      <c r="E46" s="3">
         <v>177000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>173700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>161300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>255900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>319700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>361600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>383800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>365300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>228200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>300400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>402600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>185300</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2750,50 +2852,53 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>57900</v>
+      </c>
+      <c r="E47" s="3">
         <v>89100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>114800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>144600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>83300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>51900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>39400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>50600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>105400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>135900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>105200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>42500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>63100</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2809,50 +2914,53 @@
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>88300</v>
+      </c>
+      <c r="E48" s="3">
         <v>92100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>106500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>108800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>114000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>111700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>107400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>94700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>76400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>69800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>60700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>46700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>33100</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2868,8 +2976,11 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2927,8 +3038,11 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2986,8 +3100,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3045,8 +3162,11 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3060,35 +3180,35 @@
         <v>2500</v>
       </c>
       <c r="G52" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H52" s="3">
         <v>2900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3300</v>
-      </c>
-      <c r="L52" s="3">
-        <v>3500</v>
       </c>
       <c r="M52" s="3">
         <v>3500</v>
       </c>
       <c r="N52" s="3">
+        <v>3500</v>
+      </c>
+      <c r="O52" s="3">
         <v>3800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4500</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3104,8 +3224,11 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3163,50 +3286,53 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>348500</v>
+      </c>
+      <c r="E54" s="3">
         <v>360700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>397600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>417200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>456200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>486500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>511800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>532600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>550300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>437400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>469700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>495600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>286100</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3222,8 +3348,11 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3245,8 +3374,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3268,50 +3398,51 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E57" s="3">
         <v>2700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>9900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>11600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>13400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8800</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3327,13 +3458,16 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>0</v>
+      <c r="D58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
@@ -3342,26 +3476,26 @@
         <v>0</v>
       </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>10300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1600</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3">
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M58" s="3">
         <v>1000</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3377,8 +3511,8 @@
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
+      <c r="S58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
@@ -3386,50 +3520,53 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E59" s="3">
         <v>15100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>14500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>15500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>13900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>17900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>17200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>15900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>12100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>8200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4100</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3445,50 +3582,53 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E60" s="3">
         <v>17800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>20400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>19200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>27700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>29800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>26900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>21600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>22000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>15700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>19900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>21200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>12900</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3504,8 +3644,11 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3522,32 +3665,32 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>3700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>10000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>9900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>9800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>9700</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3563,50 +3706,53 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>154600</v>
+      </c>
+      <c r="E62" s="3">
         <v>158100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>157900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>150400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>151400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>150300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>148500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>144600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>131700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>16600</v>
-      </c>
-      <c r="M62" s="3">
-        <v>17000</v>
       </c>
       <c r="N62" s="3">
         <v>17000</v>
       </c>
       <c r="O62" s="3">
+        <v>17000</v>
+      </c>
+      <c r="P62" s="3">
         <v>15600</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3622,8 +3768,11 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3681,8 +3830,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3740,8 +3892,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3799,50 +3954,53 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>170600</v>
+      </c>
+      <c r="E66" s="3">
         <v>175900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>178300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>169600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>179100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>183800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>181500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>174600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>163600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>41100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>46700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>48000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>38200</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3858,8 +4016,11 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3881,8 +4042,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3940,8 +4102,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3999,8 +4164,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4038,11 +4206,11 @@
         <v>0</v>
       </c>
       <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
         <v>339400</v>
       </c>
-      <c r="P70" s="3">
-        <v>0</v>
-      </c>
       <c r="Q70" s="3">
         <v>0</v>
       </c>
@@ -4058,8 +4226,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4117,50 +4288,53 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-683800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-655800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-616400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-583700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-550400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-519100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-487400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-456700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-425700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-388200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-360000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-334000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-310700</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4176,8 +4350,11 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4235,8 +4412,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4294,8 +4474,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4353,50 +4536,53 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>177900</v>
+      </c>
+      <c r="E76" s="3">
         <v>184800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>219200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>247600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>277200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>302700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>330200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>358000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>386700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>396200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>423000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>447600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-91600</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4412,8 +4598,11 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4471,131 +4660,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-28100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-39400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-32700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-33300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-31300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-31700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-30700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-31000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-37500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-28200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-26000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-23300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-18300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-53600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-13100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-15300</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4617,67 +4815,71 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E83" s="3">
         <v>3600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2900</v>
-      </c>
-      <c r="H83" s="3">
-        <v>2800</v>
       </c>
       <c r="I83" s="3">
         <v>2800</v>
       </c>
       <c r="J83" s="3">
+        <v>2800</v>
+      </c>
+      <c r="K83" s="3">
         <v>1700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>300</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4735,8 +4937,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4794,8 +4999,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4853,8 +5061,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4912,8 +5123,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4971,67 +5185,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-30200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-26200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-13600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-19300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-29200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-22900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-24200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-25600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>86800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-24400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-24000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-18500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-22200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-41300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-9200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-11900</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5053,67 +5273,71 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-6300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-9800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-10500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-16700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-15700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-10600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-700</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5171,8 +5395,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5230,67 +5457,73 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E94" s="3">
         <v>18600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>4200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>7000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>31300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>22700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>12500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-44000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-20600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-147100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-11600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-119000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-22800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>1700</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5312,8 +5545,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5371,8 +5605,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5430,8 +5667,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5489,8 +5729,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5548,58 +5791,61 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-10100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>400</v>
-      </c>
-      <c r="H100" s="3">
-        <v>100</v>
       </c>
       <c r="I100" s="3">
         <v>100</v>
       </c>
       <c r="J100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>26900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>224600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>193500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>47700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>9600</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
+      <c r="S100" s="3">
+        <v>0</v>
       </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
@@ -5607,8 +5853,11 @@
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5666,63 +5915,69 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-8000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-9100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-22400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-27100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-13000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>69600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-44800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-171500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>194500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>52300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-16300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-10200</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IPSC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IPSC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="92">
   <si>
     <t>IPSC</t>
   </si>
@@ -656,134 +656,138 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>800</v>
+      </c>
+      <c r="E8" s="3">
         <v>900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>300</v>
-      </c>
-      <c r="F8" s="3">
-        <v>100</v>
       </c>
       <c r="G8" s="3">
         <v>100</v>
       </c>
       <c r="H8" s="3">
+        <v>100</v>
+      </c>
+      <c r="I8" s="3">
         <v>1700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1100</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
@@ -796,8 +800,8 @@
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R8" s="3">
-        <v>0</v>
+      <c r="R8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S8" s="3">
         <v>0</v>
@@ -811,8 +815,11 @@
       <c r="V8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -873,8 +880,11 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -935,8 +945,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -959,70 +972,74 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E12" s="3">
         <v>23400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>22300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>22800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>22700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>24900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>25600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>25900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>24500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>21200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>21800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>19500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>18900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>15400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>39700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>10800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>8500</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1083,26 +1100,29 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>13100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>4000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4200</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
@@ -1113,40 +1133,43 @@
         <v>0</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>10000</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3">
         <v>4700</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>4700</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1207,8 +1230,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1228,103 +1254,107 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>35500</v>
+      </c>
+      <c r="E17" s="3">
         <v>32200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>44000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>35800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>35200</v>
-      </c>
-      <c r="H17" s="3">
-        <v>33800</v>
       </c>
       <c r="I17" s="3">
         <v>33800</v>
       </c>
       <c r="J17" s="3">
+        <v>33800</v>
+      </c>
+      <c r="K17" s="3">
         <v>34000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>32700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>38500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>28000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>25800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>23000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>18100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>53900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>13100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>15500</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-34700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-31300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-43700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-35700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-35100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-32100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-33300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-31800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-31300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-37400</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1337,23 +1367,26 @@
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R18" s="3">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3">
         <v>-13100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-15500</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1376,41 +1409,42 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E20" s="3">
         <v>3200</v>
-      </c>
-      <c r="E20" s="3">
-        <v>3500</v>
       </c>
       <c r="F20" s="3">
         <v>3500</v>
       </c>
       <c r="G20" s="3">
+        <v>3500</v>
+      </c>
+      <c r="H20" s="3">
         <v>2900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1423,56 +1457,59 @@
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R20" s="3">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>200</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-27700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-24800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-36700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-28800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-29000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-26700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-28400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-27600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-29000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-36000</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1485,23 +1522,26 @@
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3">
         <v>-12600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-15000</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1515,10 +1555,10 @@
         <v>0</v>
       </c>
       <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
         <v>100</v>
-      </c>
-      <c r="H22" s="3">
-        <v>400</v>
       </c>
       <c r="I22" s="3">
         <v>400</v>
@@ -1527,7 +1567,7 @@
         <v>400</v>
       </c>
       <c r="K22" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="L22" s="3">
         <v>300</v>
@@ -1545,16 +1585,16 @@
         <v>300</v>
       </c>
       <c r="Q22" s="3">
+        <v>300</v>
+      </c>
+      <c r="R22" s="3">
         <v>400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>100</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
-      </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
+      <c r="T22" s="3">
+        <v>0</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>3</v>
@@ -1562,70 +1602,76 @@
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-28100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-40300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-32100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-32300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-30100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-31700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-30700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-31000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-37500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-28200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-26000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-23300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-18300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-53600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-13100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-15300</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1633,20 +1679,20 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>-900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1200</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
         <v>0</v>
       </c>
@@ -1659,8 +1705,8 @@
       <c r="M24" s="3">
         <v>0</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
+      <c r="N24" s="3">
+        <v>0</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
@@ -1677,8 +1723,8 @@
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
+      <c r="T24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U24" s="3">
         <v>0</v>
@@ -1686,8 +1732,11 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1748,132 +1797,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-28100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-39400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-32700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-33300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-31300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-31700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-30700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-31000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-37500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-28200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-26000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-23300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-18300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-53600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-13100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-15300</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-28100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-39400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-32700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-33300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-31300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-31700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-30700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-31000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-37500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-28200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-26000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-23300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-18300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-53600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-13100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-15300</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1934,8 +1992,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1996,8 +2057,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2058,8 +2122,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2120,41 +2187,44 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3200</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-3500</v>
       </c>
       <c r="F32" s="3">
         <v>-3500</v>
       </c>
       <c r="G32" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="H32" s="3">
         <v>-2900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2167,85 +2237,91 @@
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R32" s="3">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-200</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-28100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-39400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-32700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-33300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-31300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-31700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-30700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-31000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-37500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-28200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-26000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-23300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-18300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-53600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-13100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-15300</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2306,137 +2382,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-28100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-39400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-32700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-33300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-31300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-31700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-30700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-31000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-37500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-28200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-26000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-23300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-18300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-53600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-13100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-15300</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2459,8 +2544,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2483,53 +2569,54 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>41500</v>
+      </c>
+      <c r="E41" s="3">
         <v>46800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>47300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>55300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>64400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>86800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>84300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>111400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>112800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>126000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>56400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>101300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>272300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>79500</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2545,53 +2632,56 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>154900</v>
+      </c>
+      <c r="E42" s="3">
         <v>145200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>125400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>114200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>92000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>164600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>231200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>244500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>266000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>235000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>166400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>193900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>125300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>103500</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2607,8 +2697,11 @@
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2669,8 +2762,11 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2731,53 +2827,56 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E45" s="3">
         <v>7800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2400</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2793,53 +2892,56 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>203500</v>
+      </c>
+      <c r="E46" s="3">
         <v>199800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>177000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>173700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>161300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>255900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>319700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>361600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>383800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>365300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>228200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>300400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>402600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>185300</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2855,53 +2957,56 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>73200</v>
+      </c>
+      <c r="E47" s="3">
         <v>57900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>89100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>114800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>144600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>83300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>51900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>39400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>50600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>105400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>135900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>105200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>42500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>63100</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2917,53 +3022,56 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>98000</v>
+      </c>
+      <c r="E48" s="3">
         <v>88300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>92100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>106500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>108800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>114000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>111700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>107400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>94700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>76400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>69800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>60700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>46700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>33100</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2979,31 +3087,34 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
-      </c>
-      <c r="E49" s="3">
-        <v>0</v>
-      </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
+        <v>38400</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
@@ -3041,8 +3152,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3103,8 +3217,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3165,13 +3282,16 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="E52" s="3">
         <v>2500</v>
@@ -3183,35 +3303,35 @@
         <v>2500</v>
       </c>
       <c r="H52" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I52" s="3">
         <v>2900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3300</v>
-      </c>
-      <c r="M52" s="3">
-        <v>3500</v>
       </c>
       <c r="N52" s="3">
         <v>3500</v>
       </c>
       <c r="O52" s="3">
+        <v>3500</v>
+      </c>
+      <c r="P52" s="3">
         <v>3800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4500</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3227,8 +3347,11 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3289,53 +3412,56 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>416400</v>
+      </c>
+      <c r="E54" s="3">
         <v>348500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>360700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>397600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>417200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>456200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>486500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>511800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>532600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>550300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>437400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>469700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>495600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>286100</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3351,8 +3477,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3375,8 +3504,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3399,8 +3529,9 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3408,44 +3539,44 @@
         <v>3400</v>
       </c>
       <c r="E57" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F57" s="3">
         <v>2700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>9900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>11600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>13400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>8800</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3461,16 +3592,19 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
+      <c r="E58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F58" s="3">
         <v>0</v>
@@ -3479,26 +3613,26 @@
         <v>0</v>
       </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>10300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1600</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M58" s="3">
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3">
         <v>1000</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3514,8 +3648,8 @@
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
+      <c r="T58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U58" s="3">
         <v>0</v>
@@ -3523,53 +3657,56 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E59" s="3">
         <v>12600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>15100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>14500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>15500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>13900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>17900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>17200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>15900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>8200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4100</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3585,53 +3722,56 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E60" s="3">
         <v>16100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>17800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>20400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>19200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>27700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>29800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>26900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>21600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>22000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>15700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>19900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>21200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>12900</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3647,8 +3787,11 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3668,32 +3811,32 @@
         <v>0</v>
       </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>3700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>10000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>9900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>9800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>9700</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3709,53 +3852,56 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>175200</v>
+      </c>
+      <c r="E62" s="3">
         <v>154600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>158100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>157900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>150400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>151400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>150300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>148500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>144600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>131700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>16600</v>
-      </c>
-      <c r="N62" s="3">
-        <v>17000</v>
       </c>
       <c r="O62" s="3">
         <v>17000</v>
       </c>
       <c r="P62" s="3">
+        <v>17000</v>
+      </c>
+      <c r="Q62" s="3">
         <v>15600</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3771,8 +3917,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3833,8 +3982,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3895,8 +4047,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3957,53 +4112,56 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>194300</v>
+      </c>
+      <c r="E66" s="3">
         <v>170600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>175900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>178300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>169600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>179100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>183800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>181500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>174600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>163600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>41100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>46700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>48000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>38200</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4019,8 +4177,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4043,8 +4204,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4105,8 +4267,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4167,8 +4332,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4209,11 +4377,11 @@
         <v>0</v>
       </c>
       <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
         <v>339400</v>
       </c>
-      <c r="Q70" s="3">
-        <v>0</v>
-      </c>
       <c r="R70" s="3">
         <v>0</v>
       </c>
@@ -4229,8 +4397,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4291,53 +4462,56 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-715000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-683800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-655800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-616400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-583700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-550400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-519100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-487400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-456700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-425700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-388200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-360000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-334000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-310700</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4353,8 +4527,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4415,8 +4592,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4477,8 +4657,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4539,53 +4722,56 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>222100</v>
+      </c>
+      <c r="E76" s="3">
         <v>177900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>184800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>219200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>247600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>277200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>302700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>330200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>358000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>386700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>396200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>423000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>447600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-91600</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4601,8 +4787,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4663,137 +4852,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-28100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-39400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-32700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-33300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-31300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-31700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-30700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-31000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-37500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-28200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-26000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-23300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-18300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-53600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-13100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-15300</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4816,70 +5014,74 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E83" s="3">
         <v>3200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2900</v>
-      </c>
-      <c r="I83" s="3">
-        <v>2800</v>
       </c>
       <c r="J83" s="3">
         <v>2800</v>
       </c>
       <c r="K83" s="3">
+        <v>2800</v>
+      </c>
+      <c r="L83" s="3">
         <v>1700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>300</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4940,8 +5142,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5002,8 +5207,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5064,8 +5272,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5126,8 +5337,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5188,70 +5402,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-27300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-30200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-26200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-13600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-19300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-29200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-22900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-24200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-25600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>86800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-24400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-24000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-18500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-22200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-41300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-9200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-11900</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5274,70 +5494,74 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-6300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-9800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-10500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-16700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-15700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-10600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-700</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5398,8 +5622,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5460,70 +5687,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-33900</v>
+      </c>
+      <c r="E94" s="3">
         <v>11500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>18600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>4200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>7000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>31300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>22700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>12500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-44000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-20600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-147100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-11600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-119000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-22800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>1700</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5546,8 +5779,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5608,8 +5842,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5670,8 +5907,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5732,8 +5972,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5794,61 +6037,64 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>56700</v>
+      </c>
+      <c r="E100" s="3">
         <v>18200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-10100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>400</v>
-      </c>
-      <c r="I100" s="3">
-        <v>100</v>
       </c>
       <c r="J100" s="3">
         <v>100</v>
       </c>
       <c r="K100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>26900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>224600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>193500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>47700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>9600</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
+      <c r="T100" s="3">
+        <v>0</v>
       </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
@@ -5856,8 +6102,11 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5918,66 +6167,72 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-8000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-9100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-22400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-27100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-13000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>69600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-44800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-171500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>194500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>52300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-16300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-10200</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IPSC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IPSC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="92">
   <si>
     <t>IPSC</t>
   </si>
@@ -656,105 +656,109 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -762,35 +766,35 @@
         <v>800</v>
       </c>
       <c r="E8" s="3">
+        <v>800</v>
+      </c>
+      <c r="F8" s="3">
         <v>900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>300</v>
-      </c>
-      <c r="G8" s="3">
-        <v>100</v>
       </c>
       <c r="H8" s="3">
         <v>100</v>
       </c>
       <c r="I8" s="3">
+        <v>100</v>
+      </c>
+      <c r="J8" s="3">
         <v>1700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1100</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
@@ -803,8 +807,8 @@
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S8" s="3">
-        <v>0</v>
+      <c r="S8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T8" s="3">
         <v>0</v>
@@ -818,31 +822,34 @@
       <c r="W8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+      <c r="D9" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E9" s="3">
+        <v>27200</v>
+      </c>
+      <c r="F9" s="3">
+        <v>23400</v>
+      </c>
+      <c r="G9" s="3">
+        <v>22300</v>
+      </c>
+      <c r="H9" s="3">
+        <v>22800</v>
+      </c>
+      <c r="I9" s="3">
+        <v>22700</v>
+      </c>
+      <c r="J9" s="3">
+        <v>24900</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -883,31 +890,34 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>-26400</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-26400</v>
+      </c>
+      <c r="F10" s="3">
+        <v>-22600</v>
+      </c>
+      <c r="G10" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="H10" s="3">
+        <v>-22600</v>
+      </c>
+      <c r="I10" s="3">
+        <v>-22600</v>
+      </c>
+      <c r="J10" s="3">
+        <v>-23200</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -948,8 +958,11 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -973,8 +986,9 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -982,64 +996,67 @@
         <v>27200</v>
       </c>
       <c r="E12" s="3">
+        <v>27200</v>
+      </c>
+      <c r="F12" s="3">
         <v>23400</v>
       </c>
-      <c r="F12" s="3">
-        <v>22300</v>
-      </c>
       <c r="G12" s="3">
-        <v>22800</v>
+        <v>23300</v>
       </c>
       <c r="H12" s="3">
+        <v>26800</v>
+      </c>
+      <c r="I12" s="3">
         <v>22700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>24900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>25600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>25900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>24500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>21200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>21800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>19500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>18900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>15400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>39700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>10800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>8500</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1103,31 +1120,34 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>13100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>4200</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1136,63 +1156,66 @@
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>10000</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R14" s="3">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3">
         <v>4700</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>4700</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>3400</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1233,8 +1256,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1255,109 +1281,113 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>35600</v>
+      </c>
+      <c r="E17" s="3">
         <v>35500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>32200</v>
       </c>
-      <c r="F17" s="3">
-        <v>44000</v>
-      </c>
       <c r="G17" s="3">
-        <v>35800</v>
+        <v>30900</v>
       </c>
       <c r="H17" s="3">
-        <v>35200</v>
+        <v>31800</v>
       </c>
       <c r="I17" s="3">
-        <v>33800</v>
+        <v>31000</v>
       </c>
       <c r="J17" s="3">
         <v>33800</v>
       </c>
       <c r="K17" s="3">
+        <v>33800</v>
+      </c>
+      <c r="L17" s="3">
         <v>34000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>32700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>38500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>28000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>25800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>23000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>18100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>53900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>13100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>15500</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-34700</v>
+        <v>-34800</v>
       </c>
       <c r="E18" s="3">
+        <v>-34800</v>
+      </c>
+      <c r="F18" s="3">
         <v>-31300</v>
       </c>
-      <c r="F18" s="3">
-        <v>-43700</v>
-      </c>
       <c r="G18" s="3">
-        <v>-35700</v>
+        <v>-30600</v>
       </c>
       <c r="H18" s="3">
-        <v>-35100</v>
+        <v>-31600</v>
       </c>
       <c r="I18" s="3">
+        <v>-30900</v>
+      </c>
+      <c r="J18" s="3">
         <v>-32100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-33300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-31800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-31300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-37400</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1370,23 +1400,26 @@
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T18" s="3">
         <v>-13100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-15500</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1410,44 +1443,45 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>3500</v>
+        <v>-300</v>
       </c>
       <c r="E20" s="3">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>2900</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
-        <v>2400</v>
+        <v>200</v>
       </c>
       <c r="J20" s="3">
+        <v>200</v>
+      </c>
+      <c r="K20" s="3">
         <v>2100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1460,59 +1494,62 @@
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S20" s="3">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>200</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-27700</v>
+        <v>-31200</v>
       </c>
       <c r="E21" s="3">
-        <v>-24800</v>
+        <v>-31300</v>
       </c>
       <c r="F21" s="3">
-        <v>-36700</v>
+        <v>-28100</v>
       </c>
       <c r="G21" s="3">
-        <v>-28800</v>
+        <v>-27100</v>
       </c>
       <c r="H21" s="3">
+        <v>-28300</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-27800</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-29400</v>
+      </c>
+      <c r="K21" s="3">
+        <v>-28400</v>
+      </c>
+      <c r="L21" s="3">
+        <v>-27600</v>
+      </c>
+      <c r="M21" s="3">
         <v>-29000</v>
       </c>
-      <c r="I21" s="3">
-        <v>-26700</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-28400</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-27600</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-29000</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-36000</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1525,43 +1562,46 @@
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3">
         <v>-12600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-15000</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G22" s="3">
         <v>0</v>
       </c>
-      <c r="H22" s="3">
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3">
         <v>100</v>
-      </c>
-      <c r="I22" s="3">
-        <v>400</v>
       </c>
       <c r="J22" s="3">
         <v>400</v>
@@ -1570,7 +1610,7 @@
         <v>400</v>
       </c>
       <c r="L22" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="M22" s="3">
         <v>300</v>
@@ -1588,16 +1628,16 @@
         <v>300</v>
       </c>
       <c r="R22" s="3">
+        <v>300</v>
+      </c>
+      <c r="S22" s="3">
         <v>400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>100</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
+      <c r="U22" s="3">
+        <v>0</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
@@ -1605,8 +1645,11 @@
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1614,64 +1657,67 @@
         <v>-31200</v>
       </c>
       <c r="E23" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="F23" s="3">
         <v>-28100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-40300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-32100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-32300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-30100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-31700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-30700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-31000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-37500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-28200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-26000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-23300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-18300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-53600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-13100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-15300</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1682,20 +1728,20 @@
         <v>0</v>
       </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>-900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1200</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
         <v>0</v>
       </c>
@@ -1708,8 +1754,8 @@
       <c r="N24" s="3">
         <v>0</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
+      <c r="O24" s="3">
+        <v>0</v>
       </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
@@ -1726,8 +1772,8 @@
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
+      <c r="U24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V24" s="3">
         <v>0</v>
@@ -1735,8 +1781,11 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1800,8 +1849,11 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1809,64 +1861,67 @@
         <v>-31200</v>
       </c>
       <c r="E26" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="F26" s="3">
         <v>-28100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-39400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-32700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-33300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-31300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-31700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-30700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-31000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-37500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-28200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-26000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-23300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-18300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-53600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-13100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-15300</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1874,64 +1929,67 @@
         <v>-31200</v>
       </c>
       <c r="E27" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="F27" s="3">
         <v>-28100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-39400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-32700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-33300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-31300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-31700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-30700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-31000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-37500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-28200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-26000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-23300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-18300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-53600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-13100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-15300</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1995,8 +2053,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2060,8 +2121,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2125,8 +2189,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2190,44 +2257,47 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-3500</v>
+        <v>300</v>
       </c>
       <c r="E32" s="3">
-        <v>-3200</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>-3500</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>-3500</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>-2900</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>-2400</v>
+        <v>-200</v>
       </c>
       <c r="J32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K32" s="3">
         <v>-2100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2240,23 +2310,26 @@
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S32" s="3">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-200</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2264,64 +2337,67 @@
         <v>-31200</v>
       </c>
       <c r="E33" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="F33" s="3">
         <v>-28100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-39400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-32700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-33300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-31300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-31700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-30700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-31000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-37500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-28200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-26000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-23300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-18300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-53600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-13100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-15300</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2385,8 +2461,11 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2394,134 +2473,140 @@
         <v>-31200</v>
       </c>
       <c r="E35" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="F35" s="3">
         <v>-28100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-39400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-32700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-33300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-31300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-31700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-30700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-31000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-37500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-28200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-26000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-23300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-18300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-53600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-13100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-15300</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2545,8 +2630,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2570,56 +2656,57 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>52600</v>
+      </c>
+      <c r="E41" s="3">
         <v>41500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>46800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>47300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>55300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>64400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>86800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>84300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>111400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>112800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>126000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>56400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>101300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>272300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>79500</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2635,56 +2722,59 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>145500</v>
+      </c>
+      <c r="E42" s="3">
         <v>154900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>145200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>125400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>114200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>92000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>164600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>231200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>244500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>266000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>235000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>166400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>193900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>125300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>103500</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2700,31 +2790,34 @@
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="H43" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="I43" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2765,31 +2858,34 @@
       <c r="W43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2830,56 +2926,59 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>7100</v>
-      </c>
-      <c r="E45" s="3">
-        <v>7800</v>
-      </c>
-      <c r="F45" s="3">
-        <v>4300</v>
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I45" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K45" s="3">
         <v>4200</v>
       </c>
-      <c r="H45" s="3">
-        <v>4900</v>
-      </c>
-      <c r="I45" s="3">
-        <v>4500</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
+        <v>5800</v>
+      </c>
+      <c r="M45" s="3">
+        <v>5000</v>
+      </c>
+      <c r="N45" s="3">
         <v>4200</v>
       </c>
-      <c r="K45" s="3">
-        <v>5800</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="O45" s="3">
+        <v>5300</v>
+      </c>
+      <c r="P45" s="3">
+        <v>5200</v>
+      </c>
+      <c r="Q45" s="3">
         <v>5000</v>
       </c>
-      <c r="M45" s="3">
-        <v>4200</v>
-      </c>
-      <c r="N45" s="3">
-        <v>5300</v>
-      </c>
-      <c r="O45" s="3">
-        <v>5200</v>
-      </c>
-      <c r="P45" s="3">
-        <v>5000</v>
-      </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2400</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2895,56 +2994,59 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>206000</v>
+      </c>
+      <c r="E46" s="3">
         <v>203500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>199800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>177000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>173700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>161300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>255900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>319700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>361600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>383800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>365300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>228200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>300400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>402600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>185300</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2960,56 +3062,59 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>46600</v>
+      </c>
+      <c r="E47" s="3">
         <v>73200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>57900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>89100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>114800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>144600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>83300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>51900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>39400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>50600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>105400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>135900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>105200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>42500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>63100</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3025,56 +3130,59 @@
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>94100</v>
+      </c>
+      <c r="E48" s="3">
         <v>98000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>88300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>92100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>106500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>108800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>114000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>111700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>107400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>94700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>76400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>69800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>60700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>46700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>33100</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3090,34 +3198,37 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>38500</v>
+      </c>
+      <c r="E49" s="3">
         <v>38400</v>
       </c>
-      <c r="E49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K49" s="3">
-        <v>0</v>
+      <c r="F49" s="3">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L49" s="3">
         <v>0</v>
@@ -3155,8 +3266,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3220,8 +3334,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3285,8 +3402,11 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3294,7 +3414,7 @@
         <v>3400</v>
       </c>
       <c r="E52" s="3">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="F52" s="3">
         <v>2500</v>
@@ -3306,35 +3426,35 @@
         <v>2500</v>
       </c>
       <c r="I52" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J52" s="3">
         <v>2900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3300</v>
-      </c>
-      <c r="N52" s="3">
-        <v>3500</v>
       </c>
       <c r="O52" s="3">
         <v>3500</v>
       </c>
       <c r="P52" s="3">
+        <v>3500</v>
+      </c>
+      <c r="Q52" s="3">
         <v>3800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4500</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3350,8 +3470,11 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3415,56 +3538,59 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>388600</v>
+      </c>
+      <c r="E54" s="3">
         <v>416400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>348500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>360700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>397600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>417200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>456200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>486500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>511800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>532600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>550300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>437400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>469700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>495600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>286100</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3480,8 +3606,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3505,8 +3634,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3530,56 +3660,57 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3400</v>
+        <v>2600</v>
       </c>
       <c r="E57" s="3">
         <v>3400</v>
       </c>
       <c r="F57" s="3">
+        <v>3400</v>
+      </c>
+      <c r="G57" s="3">
         <v>2700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>9900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>11600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>13400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>8800</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3595,47 +3726,50 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>3</v>
+      <c r="D58" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E58" s="3">
+        <v>3700</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I58" s="3">
-        <v>10300</v>
+        <v>1200</v>
       </c>
       <c r="J58" s="3">
+        <v>10900</v>
+      </c>
+      <c r="K58" s="3">
         <v>6500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1600</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N58" s="3">
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3">
         <v>1000</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3651,8 +3785,8 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
+      <c r="U58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V58" s="3">
         <v>0</v>
@@ -3660,56 +3794,59 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>15800</v>
+        <v>3800</v>
       </c>
       <c r="E59" s="3">
-        <v>12600</v>
+        <v>4700</v>
       </c>
       <c r="F59" s="3">
-        <v>15100</v>
+        <v>5100</v>
       </c>
       <c r="G59" s="3">
-        <v>14500</v>
+        <v>5000</v>
       </c>
       <c r="H59" s="3">
-        <v>15500</v>
+        <v>5400</v>
       </c>
       <c r="I59" s="3">
-        <v>13900</v>
+        <v>7700</v>
       </c>
       <c r="J59" s="3">
+        <v>7400</v>
+      </c>
+      <c r="K59" s="3">
         <v>17900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>17200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>15900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>12100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>8200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4100</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3725,56 +3862,59 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>19800</v>
+      </c>
+      <c r="E60" s="3">
         <v>19200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>16100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>17800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>20400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>19200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>27700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>29800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>26900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>21600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>22000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>15700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>19900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>21200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>12900</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3790,56 +3930,59 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>50800</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>52700</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>44300</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>46700</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>45500</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>40800</v>
       </c>
       <c r="J61" s="3">
+        <v>41200</v>
+      </c>
+      <c r="K61" s="3">
         <v>3700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>10000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>8900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>9900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>9800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>9700</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -3855,56 +3998,59 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>175200</v>
+        <v>9000</v>
       </c>
       <c r="E62" s="3">
-        <v>154600</v>
+        <v>9300</v>
       </c>
       <c r="F62" s="3">
-        <v>158100</v>
+        <v>0</v>
       </c>
       <c r="G62" s="3">
-        <v>157900</v>
+        <v>100</v>
       </c>
       <c r="H62" s="3">
-        <v>150400</v>
+        <v>200</v>
       </c>
       <c r="I62" s="3">
-        <v>151400</v>
+        <v>400</v>
       </c>
       <c r="J62" s="3">
+        <v>400</v>
+      </c>
+      <c r="K62" s="3">
         <v>150300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>148500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>144600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>131700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>16600</v>
-      </c>
-      <c r="O62" s="3">
-        <v>17000</v>
       </c>
       <c r="P62" s="3">
         <v>17000</v>
       </c>
       <c r="Q62" s="3">
+        <v>17000</v>
+      </c>
+      <c r="R62" s="3">
         <v>15600</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3920,8 +4066,11 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3985,8 +4134,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4050,8 +4202,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4115,56 +4270,59 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>192900</v>
+      </c>
+      <c r="E66" s="3">
         <v>194300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>170600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>175900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>178300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>169600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>179100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>183800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>181500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>174600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>163600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>41100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>46700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>48000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>38200</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4180,8 +4338,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4205,8 +4366,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4270,8 +4432,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4335,8 +4500,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4380,11 +4548,11 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
         <v>339400</v>
       </c>
-      <c r="R70" s="3">
-        <v>0</v>
-      </c>
       <c r="S70" s="3">
         <v>0</v>
       </c>
@@ -4400,8 +4568,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4465,56 +4636,59 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-746300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-715000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-683800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-655800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-616400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-583700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-550400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-519100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-487400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-456700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-425700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-388200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-360000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-334000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-310700</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4530,8 +4704,11 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4595,8 +4772,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4660,8 +4840,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4725,56 +4908,59 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>195700</v>
+      </c>
+      <c r="E76" s="3">
         <v>222100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>177900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>184800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>219200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>247600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>277200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>302700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>330200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>358000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>386700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>396200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>423000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>447600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-91600</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4790,8 +4976,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4855,78 +5044,84 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4934,64 +5129,67 @@
         <v>-31200</v>
       </c>
       <c r="E81" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="F81" s="3">
         <v>-28100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-39400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-32700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-33300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-31300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-31700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-30700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-31000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-37500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-28200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-26000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-23300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-18300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-53600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-13100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-15300</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5015,73 +5213,77 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>3500</v>
+        <v>3400</v>
       </c>
       <c r="E83" s="3">
         <v>3200</v>
       </c>
       <c r="F83" s="3">
-        <v>3600</v>
+        <v>2900</v>
       </c>
       <c r="G83" s="3">
-        <v>3400</v>
+        <v>2800</v>
       </c>
       <c r="H83" s="3">
-        <v>3200</v>
+        <v>2800</v>
       </c>
       <c r="I83" s="3">
-        <v>2900</v>
+        <v>1700</v>
       </c>
       <c r="J83" s="3">
-        <v>2800</v>
+        <v>1200</v>
       </c>
       <c r="K83" s="3">
         <v>2800</v>
       </c>
       <c r="L83" s="3">
+        <v>2800</v>
+      </c>
+      <c r="M83" s="3">
         <v>1700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>300</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5145,8 +5347,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5210,8 +5415,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5275,8 +5483,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5340,8 +5551,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5405,73 +5619,79 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-28300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-27300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-30200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-26200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-13600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-19300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-29200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-22900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-24200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-25600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>86800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-24400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-24000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-18500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-22200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-41300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-9200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-11900</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5495,73 +5715,77 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-6300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-9800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-10500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-16700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-15700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-10600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-700</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5625,8 +5849,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5690,73 +5917,79 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>39200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-33900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>11500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>18600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>4200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>7000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>31300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>22700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>12500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-44000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-20600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-147100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-11600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-119000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-22800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>1700</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5780,31 +6013,32 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5845,8 +6079,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5910,8 +6147,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5975,8 +6215,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6040,64 +6283,67 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>300</v>
+      </c>
+      <c r="E100" s="3">
         <v>56700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>18200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-10100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>400</v>
-      </c>
-      <c r="J100" s="3">
-        <v>100</v>
       </c>
       <c r="K100" s="3">
         <v>100</v>
       </c>
       <c r="L100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>26900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>224600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>193500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>47700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>9600</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
+      <c r="U100" s="3">
+        <v>0</v>
       </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
@@ -6105,31 +6351,34 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -6170,69 +6419,75 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-8000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-9100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-22400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-27100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-13000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>69600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-44800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-171500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>194500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>52300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-16300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-10200</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IPSC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IPSC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="92">
   <si>
     <t>IPSC</t>
   </si>
@@ -656,148 +656,151 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>800</v>
+        <v>4200</v>
       </c>
       <c r="E8" s="3">
         <v>800</v>
       </c>
       <c r="F8" s="3">
+        <v>800</v>
+      </c>
+      <c r="G8" s="3">
         <v>900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>300</v>
-      </c>
-      <c r="H8" s="3">
-        <v>100</v>
       </c>
       <c r="I8" s="3">
         <v>100</v>
       </c>
       <c r="J8" s="3">
+        <v>100</v>
+      </c>
+      <c r="K8" s="3">
         <v>1700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1100</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
@@ -810,8 +813,8 @@
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T8" s="3">
-        <v>0</v>
+      <c r="T8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U8" s="3">
         <v>0</v>
@@ -825,35 +828,38 @@
       <c r="X8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>27200</v>
+        <v>29400</v>
       </c>
       <c r="E9" s="3">
         <v>27200</v>
       </c>
       <c r="F9" s="3">
+        <v>27200</v>
+      </c>
+      <c r="G9" s="3">
         <v>23400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>22300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>22800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>22700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>24900</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
@@ -893,35 +899,38 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>-26400</v>
+        <v>-25200</v>
       </c>
       <c r="E10" s="3">
         <v>-26400</v>
       </c>
       <c r="F10" s="3">
+        <v>-26400</v>
+      </c>
+      <c r="G10" s="3">
         <v>-22600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-22000</v>
-      </c>
-      <c r="H10" s="3">
-        <v>-22600</v>
       </c>
       <c r="I10" s="3">
         <v>-22600</v>
       </c>
       <c r="J10" s="3">
+        <v>-22600</v>
+      </c>
+      <c r="K10" s="3">
         <v>-23200</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -961,8 +970,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -987,76 +999,80 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>27200</v>
+        <v>29400</v>
       </c>
       <c r="E12" s="3">
         <v>27200</v>
       </c>
       <c r="F12" s="3">
+        <v>27200</v>
+      </c>
+      <c r="G12" s="3">
         <v>23400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>23300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>26800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>22700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>24900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>25600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>25900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>24500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>21200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>21800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>19500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>18900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>15400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>39700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>10800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>8500</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1123,13 +1139,16 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>3000</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -1137,20 +1156,20 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>13100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>4000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>4200</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1159,40 +1178,43 @@
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>10000</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S14" s="3">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" s="3">
         <v>4700</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>4700</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1200,26 +1222,26 @@
         <v>3300</v>
       </c>
       <c r="E15" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F15" s="3">
         <v>3500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>3200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2900</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1259,8 +1281,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1282,115 +1307,119 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>38500</v>
+      </c>
+      <c r="E17" s="3">
         <v>35600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>35500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>32200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>30900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>31800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>31000</v>
-      </c>
-      <c r="J17" s="3">
-        <v>33800</v>
       </c>
       <c r="K17" s="3">
         <v>33800</v>
       </c>
       <c r="L17" s="3">
+        <v>33800</v>
+      </c>
+      <c r="M17" s="3">
         <v>34000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>32700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>38500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>28000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>25800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>23000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>18100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>53900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>13100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>15500</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-34800</v>
+        <v>-34300</v>
       </c>
       <c r="E18" s="3">
         <v>-34800</v>
       </c>
       <c r="F18" s="3">
+        <v>-34800</v>
+      </c>
+      <c r="G18" s="3">
         <v>-31300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-30600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-31600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-30900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-32100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-33300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-31800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-31300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-37400</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1403,23 +1432,26 @@
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T18" s="3">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U18" s="3">
         <v>-13100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-15500</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1444,17 +1476,18 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-300</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
@@ -1465,26 +1498,26 @@
         <v>0</v>
       </c>
       <c r="I20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
         <v>200</v>
       </c>
       <c r="K20" s="3">
+        <v>200</v>
+      </c>
+      <c r="L20" s="3">
         <v>2100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1497,62 +1530,65 @@
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T20" s="3">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>200</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-30900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-31200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-31300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-28100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-27100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-28300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-27800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-29400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-28400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-27600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-29000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-36000</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1565,23 +1601,26 @@
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U21" s="3">
         <v>-12600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-15000</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1594,17 +1633,17 @@
       <c r="F22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3">
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3">
         <v>100</v>
-      </c>
-      <c r="J22" s="3">
-        <v>400</v>
       </c>
       <c r="K22" s="3">
         <v>400</v>
@@ -1613,7 +1652,7 @@
         <v>400</v>
       </c>
       <c r="M22" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="N22" s="3">
         <v>300</v>
@@ -1631,16 +1670,16 @@
         <v>300</v>
       </c>
       <c r="S22" s="3">
+        <v>300</v>
+      </c>
+      <c r="T22" s="3">
         <v>400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>100</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
-      </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
+      <c r="V22" s="3">
+        <v>0</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>3</v>
@@ -1648,81 +1687,87 @@
       <c r="X22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-31200</v>
+        <v>-34300</v>
       </c>
       <c r="E23" s="3">
         <v>-31200</v>
       </c>
       <c r="F23" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="G23" s="3">
         <v>-28100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-40300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-32100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-32300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-30100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-31700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-30700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-31000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-37500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-28200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-26000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-23300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-18300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-53600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-13100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-15300</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
@@ -1731,20 +1776,20 @@
         <v>0</v>
       </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>-900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1200</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
         <v>0</v>
       </c>
@@ -1757,8 +1802,8 @@
       <c r="O24" s="3">
         <v>0</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
+      <c r="P24" s="3">
+        <v>0</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
@@ -1775,8 +1820,8 @@
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
+      <c r="V24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W24" s="3">
         <v>0</v>
@@ -1784,8 +1829,11 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1852,144 +1900,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-31200</v>
+        <v>-36100</v>
       </c>
       <c r="E26" s="3">
         <v>-31200</v>
       </c>
       <c r="F26" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="G26" s="3">
         <v>-28100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-39400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-32700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-33300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-31300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-31700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-30700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-31000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-37500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-28200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-26000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-23300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-18300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-53600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-13100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-15300</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-31200</v>
+        <v>-36100</v>
       </c>
       <c r="E27" s="3">
         <v>-31200</v>
       </c>
       <c r="F27" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="G27" s="3">
         <v>-28100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-39400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-32700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-33300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-31300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-31700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-30700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-31000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-37500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-28200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-26000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-23300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-18300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-53600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-13100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-15300</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2056,8 +2113,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2124,8 +2184,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2192,8 +2255,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2260,17 +2326,20 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>100</v>
+      </c>
+      <c r="E32" s="3">
         <v>300</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
@@ -2281,26 +2350,26 @@
         <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
         <v>-200</v>
       </c>
       <c r="K32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L32" s="3">
         <v>-2100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2313,91 +2382,97 @@
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T32" s="3">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-200</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-31200</v>
+        <v>-36100</v>
       </c>
       <c r="E33" s="3">
         <v>-31200</v>
       </c>
       <c r="F33" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="G33" s="3">
         <v>-28100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-39400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-32700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-33300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-31300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-31700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-30700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-31000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-37500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-28200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-26000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-23300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-18300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-53600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-13100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-15300</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2464,149 +2539,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-31200</v>
+        <v>-36100</v>
       </c>
       <c r="E35" s="3">
         <v>-31200</v>
       </c>
       <c r="F35" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="G35" s="3">
         <v>-28100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-39400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-32700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-33300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-31300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-31700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-30700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-31000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-37500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-28200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-26000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-23300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-18300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-53600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-13100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-15300</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2631,8 +2715,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2657,59 +2742,60 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>58400</v>
+      </c>
+      <c r="E41" s="3">
         <v>52600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>41500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>46800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>47300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>55300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>64400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>86800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>84300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>111400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>112800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>126000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>56400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>101300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>272300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>79500</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2725,59 +2811,62 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>130900</v>
+      </c>
+      <c r="E42" s="3">
         <v>145500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>154900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>145200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>125400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>114200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>92000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>164600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>231200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>244500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>266000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>235000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>166400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>193900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>125300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>103500</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2793,35 +2882,38 @@
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E43" s="3">
         <v>1300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2200</v>
-      </c>
-      <c r="H43" s="3">
-        <v>1700</v>
       </c>
       <c r="I43" s="3">
         <v>1700</v>
       </c>
       <c r="J43" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K43" s="3">
         <v>1500</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
       <c r="L43" s="3">
         <v>0</v>
       </c>
@@ -2861,8 +2953,11 @@
       <c r="X43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2887,8 +2982,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2929,13 +3024,16 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3">
+        <v>1700</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>3</v>
@@ -2943,45 +3041,45 @@
       <c r="F45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3">
         <v>1300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2400</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2997,59 +3095,62 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>194100</v>
+      </c>
+      <c r="E46" s="3">
         <v>206000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>203500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>199800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>177000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>173700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>161300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>255900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>319700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>361600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>383800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>365300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>228200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>300400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>402600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>185300</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3065,59 +3166,62 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>30800</v>
+      </c>
+      <c r="E47" s="3">
         <v>46600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>73200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>57900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>89100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>114800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>144600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>83300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>51900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>39400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>50600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>105400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>135900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>105200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>42500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>63100</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3133,59 +3237,62 @@
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>90800</v>
+      </c>
+      <c r="E48" s="3">
         <v>94100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>98000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>88300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>92100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>106500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>108800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>114000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>111700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>107400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>94700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>76400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>69800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>60700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>46700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>33100</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3201,20 +3308,23 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>34200</v>
+      </c>
+      <c r="E49" s="3">
         <v>38500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>38400</v>
       </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
       <c r="G49" s="3">
         <v>0</v>
       </c>
@@ -3227,11 +3337,11 @@
       <c r="J49" s="3">
         <v>0</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L49" s="3">
-        <v>0</v>
+      <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M49" s="3">
         <v>0</v>
@@ -3269,8 +3379,11 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3337,8 +3450,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3405,19 +3521,22 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>3400</v>
+        <v>3300</v>
       </c>
       <c r="E52" s="3">
         <v>3400</v>
       </c>
       <c r="F52" s="3">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="G52" s="3">
         <v>2500</v>
@@ -3429,35 +3548,35 @@
         <v>2500</v>
       </c>
       <c r="J52" s="3">
+        <v>2500</v>
+      </c>
+      <c r="K52" s="3">
         <v>2900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3300</v>
-      </c>
-      <c r="O52" s="3">
-        <v>3500</v>
       </c>
       <c r="P52" s="3">
         <v>3500</v>
       </c>
       <c r="Q52" s="3">
+        <v>3500</v>
+      </c>
+      <c r="R52" s="3">
         <v>3800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4500</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3473,8 +3592,11 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3541,59 +3663,62 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>353200</v>
+      </c>
+      <c r="E54" s="3">
         <v>388600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>416400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>348500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>360700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>397600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>417200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>456200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>486500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>511800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>532600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>550300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>437400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>469700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>495600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>286100</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3609,8 +3734,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3635,8 +3763,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3661,59 +3790,60 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E57" s="3">
         <v>2600</v>
-      </c>
-      <c r="E57" s="3">
-        <v>3400</v>
       </c>
       <c r="F57" s="3">
         <v>3400</v>
       </c>
       <c r="G57" s="3">
+        <v>3400</v>
+      </c>
+      <c r="H57" s="3">
         <v>2700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>9900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>7600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>11600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>13400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>8800</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3729,50 +3859,53 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E58" s="3">
         <v>3800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>10900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1600</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O58" s="3">
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P58" s="3">
         <v>1000</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3788,8 +3921,8 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
+      <c r="V58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W58" s="3">
         <v>0</v>
@@ -3797,59 +3930,62 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>109200</v>
+      </c>
+      <c r="E59" s="3">
         <v>3800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>17900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>17200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>15900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>12100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>8200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>7800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4100</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3865,59 +4001,62 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>129800</v>
+      </c>
+      <c r="E60" s="3">
         <v>19800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>19200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>16100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>17800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>20400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>19200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>27700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>29800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>26900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>21600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>22000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>15700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>19900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>21200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>12900</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3933,59 +4072,62 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>49000</v>
+      </c>
+      <c r="E61" s="3">
         <v>50800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>52700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>44300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>46700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>45500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>40800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>41200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>10000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>8900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>9900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>9800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>9700</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4001,59 +4143,62 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E62" s="3">
         <v>9000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>9300</v>
       </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
       <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3">
         <v>100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>200</v>
-      </c>
-      <c r="I62" s="3">
-        <v>400</v>
       </c>
       <c r="J62" s="3">
         <v>400</v>
       </c>
       <c r="K62" s="3">
+        <v>400</v>
+      </c>
+      <c r="L62" s="3">
         <v>150300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>148500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>144600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>131700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>16600</v>
-      </c>
-      <c r="P62" s="3">
-        <v>17000</v>
       </c>
       <c r="Q62" s="3">
         <v>17000</v>
       </c>
       <c r="R62" s="3">
+        <v>17000</v>
+      </c>
+      <c r="S62" s="3">
         <v>15600</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4069,8 +4214,11 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4137,8 +4285,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4205,8 +4356,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4273,59 +4427,62 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>191900</v>
+      </c>
+      <c r="E66" s="3">
         <v>192900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>194300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>170600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>175900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>178300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>169600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>179100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>183800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>181500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>174600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>163600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>41100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>46700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>48000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>38200</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4341,8 +4498,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4367,8 +4527,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4435,8 +4596,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4503,8 +4667,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4551,11 +4718,11 @@
         <v>0</v>
       </c>
       <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
         <v>339400</v>
       </c>
-      <c r="S70" s="3">
-        <v>0</v>
-      </c>
       <c r="T70" s="3">
         <v>0</v>
       </c>
@@ -4571,8 +4738,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4639,59 +4809,62 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-782300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-746300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-715000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-683800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-655800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-616400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-583700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-550400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-519100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-487400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-456700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-425700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-388200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-360000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-334000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-310700</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4707,8 +4880,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4775,8 +4951,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4843,8 +5022,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4911,59 +5093,62 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>161400</v>
+      </c>
+      <c r="E76" s="3">
         <v>195700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>222100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>177900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>184800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>219200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>247600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>277200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>302700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>330200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>358000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>386700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>396200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>423000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>447600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-91600</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4979,8 +5164,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5047,149 +5235,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-31200</v>
+        <v>-36100</v>
       </c>
       <c r="E81" s="3">
         <v>-31200</v>
       </c>
       <c r="F81" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="G81" s="3">
         <v>-28100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-39400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-32700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-33300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-31300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-31700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-30700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-31000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-37500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-28200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-26000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-23300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-18300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-53600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-13100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-15300</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5214,76 +5411,80 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E83" s="3">
         <v>3400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2900</v>
-      </c>
-      <c r="G83" s="3">
-        <v>2800</v>
       </c>
       <c r="H83" s="3">
         <v>2800</v>
       </c>
       <c r="I83" s="3">
+        <v>2800</v>
+      </c>
+      <c r="J83" s="3">
         <v>1700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1200</v>
-      </c>
-      <c r="K83" s="3">
-        <v>2800</v>
       </c>
       <c r="L83" s="3">
         <v>2800</v>
       </c>
       <c r="M83" s="3">
+        <v>2800</v>
+      </c>
+      <c r="N83" s="3">
         <v>1700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>300</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5350,8 +5551,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5418,8 +5622,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5486,8 +5693,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5554,8 +5764,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5622,76 +5835,82 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-24200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-28300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-27300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-30200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-26200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-13600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-19300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-29200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-22900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-24200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-25600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>86800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-24400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-24000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-18500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-22200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-41300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-9200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-11900</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5716,76 +5935,80 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E91" s="3">
         <v>800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-9800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-10500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-16700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-15700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-10600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-700</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5852,8 +6075,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5920,76 +6146,82 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E94" s="3">
         <v>39200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-33900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>11500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>18600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>4200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>7000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>31300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>22700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>12500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-44000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-20600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-147100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-11600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-119000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-22800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>1700</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6014,8 +6246,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6040,8 +6273,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6082,8 +6315,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6150,8 +6386,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6218,8 +6457,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6286,67 +6528,70 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E100" s="3">
         <v>300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>56700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>18200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-10100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>400</v>
-      </c>
-      <c r="K100" s="3">
-        <v>100</v>
       </c>
       <c r="L100" s="3">
         <v>100</v>
       </c>
       <c r="M100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>26900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>224600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>193500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>47700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>9600</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
+      <c r="V100" s="3">
+        <v>0</v>
       </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
@@ -6354,8 +6599,11 @@
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6380,8 +6628,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -6422,72 +6670,78 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E102" s="3">
         <v>11100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-8000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-9100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-22400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-27100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-13000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>69600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-44800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-171500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>194500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>52300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-16300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-10200</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IPSC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IPSC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="92">
   <si>
     <t>IPSC</t>
   </si>
@@ -656,154 +656,158 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>109200</v>
+      </c>
+      <c r="E8" s="3">
         <v>4200</v>
-      </c>
-      <c r="E8" s="3">
-        <v>800</v>
       </c>
       <c r="F8" s="3">
         <v>800</v>
       </c>
       <c r="G8" s="3">
+        <v>800</v>
+      </c>
+      <c r="H8" s="3">
         <v>900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>300</v>
-      </c>
-      <c r="I8" s="3">
-        <v>100</v>
       </c>
       <c r="J8" s="3">
         <v>100</v>
       </c>
       <c r="K8" s="3">
+        <v>100</v>
+      </c>
+      <c r="L8" s="3">
         <v>1700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1100</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
@@ -816,8 +820,8 @@
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U8" s="3">
-        <v>0</v>
+      <c r="U8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V8" s="3">
         <v>0</v>
@@ -831,38 +835,41 @@
       <c r="Y8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>26600</v>
+      </c>
+      <c r="E9" s="3">
         <v>29400</v>
-      </c>
-      <c r="E9" s="3">
-        <v>27200</v>
       </c>
       <c r="F9" s="3">
         <v>27200</v>
       </c>
       <c r="G9" s="3">
+        <v>27200</v>
+      </c>
+      <c r="H9" s="3">
         <v>23400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>22300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>22800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>22700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>24900</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -902,38 +909,41 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>82600</v>
+      </c>
+      <c r="E10" s="3">
         <v>-25200</v>
-      </c>
-      <c r="E10" s="3">
-        <v>-26400</v>
       </c>
       <c r="F10" s="3">
         <v>-26400</v>
       </c>
       <c r="G10" s="3">
+        <v>-26400</v>
+      </c>
+      <c r="H10" s="3">
         <v>-22600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-22000</v>
-      </c>
-      <c r="I10" s="3">
-        <v>-22600</v>
       </c>
       <c r="J10" s="3">
         <v>-22600</v>
       </c>
       <c r="K10" s="3">
+        <v>-22600</v>
+      </c>
+      <c r="L10" s="3">
         <v>-23200</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -973,8 +983,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1000,79 +1013,83 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>26600</v>
+      </c>
+      <c r="E12" s="3">
         <v>29400</v>
-      </c>
-      <c r="E12" s="3">
-        <v>27200</v>
       </c>
       <c r="F12" s="3">
         <v>27200</v>
       </c>
       <c r="G12" s="3">
+        <v>27200</v>
+      </c>
+      <c r="H12" s="3">
         <v>23400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>23300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>26800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>22700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>24900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>25600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>25900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>24500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>21200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>21800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>19500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>18900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>15400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>39700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>10800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>8500</v>
       </c>
-      <c r="W12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1142,37 +1159,40 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>3000</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>13100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>4000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>4200</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1181,70 +1201,73 @@
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>10000</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U14" s="3">
         <v>4700</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>4700</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>3300</v>
+        <v>3200</v>
       </c>
       <c r="E15" s="3">
         <v>3300</v>
       </c>
       <c r="F15" s="3">
+        <v>3300</v>
+      </c>
+      <c r="G15" s="3">
         <v>3500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2900</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1284,8 +1307,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1308,121 +1334,125 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>35000</v>
+      </c>
+      <c r="E17" s="3">
         <v>38500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>35600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>35500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>32200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>30900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>31800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>31000</v>
-      </c>
-      <c r="K17" s="3">
-        <v>33800</v>
       </c>
       <c r="L17" s="3">
         <v>33800</v>
       </c>
       <c r="M17" s="3">
+        <v>33800</v>
+      </c>
+      <c r="N17" s="3">
         <v>34000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>32700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>38500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>28000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>25800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>23000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>18100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>53900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>13100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>15500</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>74200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-34300</v>
-      </c>
-      <c r="E18" s="3">
-        <v>-34800</v>
       </c>
       <c r="F18" s="3">
         <v>-34800</v>
       </c>
       <c r="G18" s="3">
+        <v>-34800</v>
+      </c>
+      <c r="H18" s="3">
         <v>-31300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-30600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-31600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-30900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-32100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-33300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-31800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-31300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-37400</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1435,23 +1465,26 @@
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V18" s="3">
         <v>-13100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-15500</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1477,20 +1510,21 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-300</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
@@ -1501,26 +1535,26 @@
         <v>0</v>
       </c>
       <c r="J20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3">
         <v>200</v>
       </c>
       <c r="L20" s="3">
+        <v>200</v>
+      </c>
+      <c r="M20" s="3">
         <v>2100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1533,65 +1567,68 @@
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>200</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>77400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-30900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-31200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-31300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-28100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-27100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-28300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-27800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-29400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-28400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-27600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-29000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-36000</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1604,23 +1641,26 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V21" s="3">
         <v>-12600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-15000</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1636,17 +1676,17 @@
       <c r="G22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="3">
         <v>100</v>
-      </c>
-      <c r="K22" s="3">
-        <v>400</v>
       </c>
       <c r="L22" s="3">
         <v>400</v>
@@ -1655,7 +1695,7 @@
         <v>400</v>
       </c>
       <c r="N22" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O22" s="3">
         <v>300</v>
@@ -1673,16 +1713,16 @@
         <v>300</v>
       </c>
       <c r="T22" s="3">
+        <v>300</v>
+      </c>
+      <c r="U22" s="3">
         <v>400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>100</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
-      </c>
-      <c r="W22" s="3" t="s">
-        <v>3</v>
+      <c r="W22" s="3">
+        <v>0</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>3</v>
@@ -1690,88 +1730,94 @@
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>76600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-34300</v>
-      </c>
-      <c r="E23" s="3">
-        <v>-31200</v>
       </c>
       <c r="F23" s="3">
         <v>-31200</v>
       </c>
       <c r="G23" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="H23" s="3">
         <v>-28100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-40300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-32100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-32300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-30100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-31700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-30700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-31000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-37500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-28200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-26000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-23300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-18300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-53600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-13100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-15300</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3">
         <v>1800</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
         <v>0</v>
       </c>
@@ -1779,20 +1825,20 @@
         <v>0</v>
       </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>-900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1200</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
@@ -1805,8 +1851,8 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
+      <c r="Q24" s="3">
+        <v>0</v>
       </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
@@ -1823,8 +1869,8 @@
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
+      <c r="W24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X24" s="3">
         <v>0</v>
@@ -1832,8 +1878,11 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1903,150 +1952,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>76600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-36100</v>
-      </c>
-      <c r="E26" s="3">
-        <v>-31200</v>
       </c>
       <c r="F26" s="3">
         <v>-31200</v>
       </c>
       <c r="G26" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="H26" s="3">
         <v>-28100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-39400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-32700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-33300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-31300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-31700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-30700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-31000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-37500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-28200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-26000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-23300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-18300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-53600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-13100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-15300</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>76600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-36100</v>
-      </c>
-      <c r="E27" s="3">
-        <v>-31200</v>
       </c>
       <c r="F27" s="3">
         <v>-31200</v>
       </c>
       <c r="G27" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="H27" s="3">
         <v>-28100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-39400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-32700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-33300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-31300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-31700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-30700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-31000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-37500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-28200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-26000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-23300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-18300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-53600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-13100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-15300</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2116,8 +2174,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2187,8 +2248,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2258,8 +2322,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2329,20 +2396,23 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>300</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
@@ -2353,26 +2423,26 @@
         <v>0</v>
       </c>
       <c r="J32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="K32" s="3">
         <v>-200</v>
       </c>
       <c r="L32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M32" s="3">
         <v>-2100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2385,94 +2455,100 @@
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-200</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>76600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-36100</v>
-      </c>
-      <c r="E33" s="3">
-        <v>-31200</v>
       </c>
       <c r="F33" s="3">
         <v>-31200</v>
       </c>
       <c r="G33" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="H33" s="3">
         <v>-28100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-39400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-32700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-33300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-31300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-31700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-30700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-31000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-37500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-28200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-26000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-23300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-18300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-53600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-13100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-15300</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2542,155 +2618,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>76600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-36100</v>
-      </c>
-      <c r="E35" s="3">
-        <v>-31200</v>
       </c>
       <c r="F35" s="3">
         <v>-31200</v>
       </c>
       <c r="G35" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="H35" s="3">
         <v>-28100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-39400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-32700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-33300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-31300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-31700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-30700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-31000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-37500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-28200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-26000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-23300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-18300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-53600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-13100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-15300</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2716,8 +2801,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2743,62 +2829,63 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>51900</v>
+      </c>
+      <c r="E41" s="3">
         <v>58400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>52600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>41500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>46800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>47300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>55300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>64400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>86800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>84300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>111400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>112800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>126000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>56400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>101300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>272300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>79500</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2814,62 +2901,65 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>113300</v>
+      </c>
+      <c r="E42" s="3">
         <v>130900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>145500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>154900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>145200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>125400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>114200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>92000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>164600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>231200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>244500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>266000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>235000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>166400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>193900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>125300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>103500</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2885,38 +2975,41 @@
       <c r="Y42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2200</v>
-      </c>
-      <c r="I43" s="3">
-        <v>1700</v>
       </c>
       <c r="J43" s="3">
         <v>1700</v>
       </c>
       <c r="K43" s="3">
+        <v>1700</v>
+      </c>
+      <c r="L43" s="3">
         <v>1500</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
       <c r="M43" s="3">
         <v>0</v>
       </c>
@@ -2956,8 +3049,11 @@
       <c r="Y43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2985,8 +3081,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3027,62 +3123,65 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3">
         <v>1700</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3">
         <v>1300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2400</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3098,62 +3197,65 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>169600</v>
+      </c>
+      <c r="E46" s="3">
         <v>194100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>206000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>203500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>199800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>177000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>173700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>161300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>255900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>319700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>361600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>383800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>365300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>228200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>300400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>402600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>185300</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3169,62 +3271,65 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E47" s="3">
         <v>30800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>46600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>73200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>57900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>89100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>114800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>144600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>83300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>51900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>39400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>50600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>105400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>135900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>105200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>42500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>63100</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3240,62 +3345,65 @@
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>87800</v>
+      </c>
+      <c r="E48" s="3">
         <v>90800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>94100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>98000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>88300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>92100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>106500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>108800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>114000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>111700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>107400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>94700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>76400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>69800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>60700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>46700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>33100</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3311,8 +3419,11 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3320,14 +3431,14 @@
         <v>34200</v>
       </c>
       <c r="E49" s="3">
+        <v>34200</v>
+      </c>
+      <c r="F49" s="3">
         <v>38500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>38400</v>
       </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
       <c r="H49" s="3">
         <v>0</v>
       </c>
@@ -3340,11 +3451,11 @@
       <c r="K49" s="3">
         <v>0</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M49" s="3">
-        <v>0</v>
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N49" s="3">
         <v>0</v>
@@ -3382,8 +3493,11 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3453,8 +3567,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3524,8 +3641,11 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3533,13 +3653,13 @@
         <v>3300</v>
       </c>
       <c r="E52" s="3">
-        <v>3400</v>
+        <v>3300</v>
       </c>
       <c r="F52" s="3">
         <v>3400</v>
       </c>
       <c r="G52" s="3">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="H52" s="3">
         <v>2500</v>
@@ -3551,35 +3671,35 @@
         <v>2500</v>
       </c>
       <c r="K52" s="3">
+        <v>2500</v>
+      </c>
+      <c r="L52" s="3">
         <v>2900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3300</v>
-      </c>
-      <c r="P52" s="3">
-        <v>3500</v>
       </c>
       <c r="Q52" s="3">
         <v>3500</v>
       </c>
       <c r="R52" s="3">
+        <v>3500</v>
+      </c>
+      <c r="S52" s="3">
         <v>3800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4500</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3595,8 +3715,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3666,62 +3789,65 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>315600</v>
+      </c>
+      <c r="E54" s="3">
         <v>353200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>388600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>416400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>348500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>360700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>397600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>417200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>456200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>486500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>511800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>532600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>550300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>437400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>469700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>495600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>286100</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3737,8 +3863,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3764,8 +3893,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3791,62 +3921,63 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E57" s="3">
         <v>3100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2600</v>
-      </c>
-      <c r="F57" s="3">
-        <v>3400</v>
       </c>
       <c r="G57" s="3">
         <v>3400</v>
       </c>
       <c r="H57" s="3">
+        <v>3400</v>
+      </c>
+      <c r="I57" s="3">
         <v>2700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>9900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>7600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>11600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>13400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>8800</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3862,8 +3993,11 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3871,44 +4005,44 @@
         <v>4900</v>
       </c>
       <c r="E58" s="3">
+        <v>4900</v>
+      </c>
+      <c r="F58" s="3">
         <v>3800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>10900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1600</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P58" s="3">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3">
         <v>1000</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3924,8 +4058,8 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
+      <c r="W58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X58" s="3">
         <v>0</v>
@@ -3933,62 +4067,65 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3">
         <v>109200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>17900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>17200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>15900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>12100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>8200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>7800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4100</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4004,62 +4141,65 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E60" s="3">
         <v>129800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>19800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>19200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>16100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>17800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>20400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>19200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>27700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>29800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>26900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>21600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>22000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>15700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>19900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>21200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>12900</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4075,62 +4215,65 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>47800</v>
+      </c>
+      <c r="E61" s="3">
         <v>49000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>50800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>52700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>44300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>46700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>45500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>40800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>41200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>8500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>10000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>8900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>9900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>9800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>9700</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4146,62 +4289,65 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E62" s="3">
         <v>8700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>9000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>9300</v>
       </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
       <c r="H62" s="3">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3">
         <v>100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>200</v>
-      </c>
-      <c r="J62" s="3">
-        <v>400</v>
       </c>
       <c r="K62" s="3">
         <v>400</v>
       </c>
       <c r="L62" s="3">
+        <v>400</v>
+      </c>
+      <c r="M62" s="3">
         <v>150300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>148500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>144600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>131700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>16600</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>17000</v>
       </c>
       <c r="R62" s="3">
         <v>17000</v>
       </c>
       <c r="S62" s="3">
+        <v>17000</v>
+      </c>
+      <c r="T62" s="3">
         <v>15600</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4217,8 +4363,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4288,8 +4437,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4359,8 +4511,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4430,62 +4585,65 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>75200</v>
+      </c>
+      <c r="E66" s="3">
         <v>191900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>192900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>194300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>170600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>175900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>178300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>169600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>179100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>183800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>181500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>174600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>163600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>41100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>46700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>48000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>38200</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4501,8 +4659,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4528,8 +4689,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4599,8 +4761,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4670,8 +4835,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4721,11 +4889,11 @@
         <v>0</v>
       </c>
       <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
         <v>339400</v>
       </c>
-      <c r="T70" s="3">
-        <v>0</v>
-      </c>
       <c r="U70" s="3">
         <v>0</v>
       </c>
@@ -4741,8 +4909,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4812,62 +4983,65 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-705800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-782300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-746300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-715000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-683800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-655800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-616400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-583700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-550400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-519100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-487400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-456700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-425700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-388200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-360000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-334000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-310700</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4883,8 +5057,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4954,8 +5131,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5025,8 +5205,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5096,62 +5279,65 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>240400</v>
+      </c>
+      <c r="E76" s="3">
         <v>161400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>195700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>222100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>177900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>184800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>219200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>247600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>277200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>302700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>330200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>358000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>386700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>396200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>423000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>447600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-91600</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5167,8 +5353,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5238,155 +5427,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>76600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-36100</v>
-      </c>
-      <c r="E81" s="3">
-        <v>-31200</v>
       </c>
       <c r="F81" s="3">
         <v>-31200</v>
       </c>
       <c r="G81" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="H81" s="3">
         <v>-28100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-39400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-32700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-33300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-31300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-31700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-30700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-31000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-37500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-28200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-26000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-23300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-18300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-53600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-13100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-15300</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5412,79 +5610,83 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E83" s="3">
         <v>3600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2900</v>
-      </c>
-      <c r="H83" s="3">
-        <v>2800</v>
       </c>
       <c r="I83" s="3">
         <v>2800</v>
       </c>
       <c r="J83" s="3">
+        <v>2800</v>
+      </c>
+      <c r="K83" s="3">
         <v>1700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1200</v>
-      </c>
-      <c r="L83" s="3">
-        <v>2800</v>
       </c>
       <c r="M83" s="3">
         <v>2800</v>
       </c>
       <c r="N83" s="3">
+        <v>2800</v>
+      </c>
+      <c r="O83" s="3">
         <v>1700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>300</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5554,8 +5756,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5625,8 +5830,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5696,8 +5904,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5767,8 +5978,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5838,79 +6052,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-34600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-24200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-28300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-27300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-30200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-26200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-13600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-19300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-29200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-22900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-24200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-25600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>86800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-24400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-24000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-18500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-22200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-41300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-9200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-11900</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5936,79 +6156,83 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-9800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-10500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-16700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-15700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-10600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-700</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6078,8 +6302,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6149,79 +6376,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E94" s="3">
         <v>30600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>39200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-33900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>11500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>18600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>4200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>7000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>31300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>22700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>12500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-44000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-20600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-147100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-11600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-119000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-22800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>1700</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6247,8 +6480,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6276,8 +6510,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6318,8 +6552,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6389,8 +6626,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6460,8 +6700,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6531,70 +6774,73 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>56700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>18200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-10100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>400</v>
-      </c>
-      <c r="L100" s="3">
-        <v>100</v>
       </c>
       <c r="M100" s="3">
         <v>100</v>
       </c>
       <c r="N100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>26900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>224600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>193500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>47700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>9600</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
+      <c r="W100" s="3">
+        <v>0</v>
       </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
@@ -6602,8 +6848,11 @@
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6631,8 +6880,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -6673,75 +6922,81 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E102" s="3">
         <v>5800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>11100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-8000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-9100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-22400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-27100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-13000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>69600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-44800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-171500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>194500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>52300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-16300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-10200</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IPSC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IPSC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="92">
   <si>
     <t>IPSC</t>
   </si>
@@ -656,161 +656,165 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3">
         <v>109200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4200</v>
-      </c>
-      <c r="F8" s="3">
-        <v>800</v>
       </c>
       <c r="G8" s="3">
         <v>800</v>
       </c>
       <c r="H8" s="3">
+        <v>800</v>
+      </c>
+      <c r="I8" s="3">
         <v>900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>300</v>
-      </c>
-      <c r="J8" s="3">
-        <v>100</v>
       </c>
       <c r="K8" s="3">
         <v>100</v>
       </c>
       <c r="L8" s="3">
+        <v>100</v>
+      </c>
+      <c r="M8" s="3">
         <v>1700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1100</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
@@ -823,8 +827,8 @@
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V8" s="3">
-        <v>0</v>
+      <c r="V8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W8" s="3">
         <v>0</v>
@@ -838,41 +842,44 @@
       <c r="Z8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>26900</v>
+      </c>
+      <c r="E9" s="3">
         <v>26600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>29400</v>
-      </c>
-      <c r="F9" s="3">
-        <v>27200</v>
       </c>
       <c r="G9" s="3">
         <v>27200</v>
       </c>
       <c r="H9" s="3">
+        <v>27200</v>
+      </c>
+      <c r="I9" s="3">
         <v>23400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>22300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>22800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>22700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>24900</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
@@ -912,41 +919,44 @@
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="E10" s="3">
         <v>82600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-25200</v>
-      </c>
-      <c r="F10" s="3">
-        <v>-26400</v>
       </c>
       <c r="G10" s="3">
         <v>-26400</v>
       </c>
       <c r="H10" s="3">
+        <v>-26400</v>
+      </c>
+      <c r="I10" s="3">
         <v>-22600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-22000</v>
-      </c>
-      <c r="J10" s="3">
-        <v>-22600</v>
       </c>
       <c r="K10" s="3">
         <v>-22600</v>
       </c>
       <c r="L10" s="3">
+        <v>-22600</v>
+      </c>
+      <c r="M10" s="3">
         <v>-23200</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -986,8 +996,11 @@
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1014,82 +1027,86 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>26900</v>
+      </c>
+      <c r="E12" s="3">
         <v>26600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>29400</v>
-      </c>
-      <c r="F12" s="3">
-        <v>27200</v>
       </c>
       <c r="G12" s="3">
         <v>27200</v>
       </c>
       <c r="H12" s="3">
+        <v>27200</v>
+      </c>
+      <c r="I12" s="3">
         <v>23400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>23300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>26800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>22700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>24900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>25600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>25900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>24500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>21200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>21800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>19500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>18900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>15400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>39700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>10800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>8500</v>
       </c>
-      <c r="X12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1162,40 +1179,43 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>3000</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>13100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>4000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4200</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1204,40 +1224,43 @@
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>10000</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V14" s="3">
         <v>4700</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>4700</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1245,32 +1268,32 @@
         <v>3200</v>
       </c>
       <c r="E15" s="3">
-        <v>3300</v>
+        <v>3200</v>
       </c>
       <c r="F15" s="3">
         <v>3300</v>
       </c>
       <c r="G15" s="3">
+        <v>3300</v>
+      </c>
+      <c r="H15" s="3">
         <v>3500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2900</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1310,8 +1333,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1335,127 +1361,131 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>34700</v>
+      </c>
+      <c r="E17" s="3">
         <v>35000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>38500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>35600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>35500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>32200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>30900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>31800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>31000</v>
-      </c>
-      <c r="L17" s="3">
-        <v>33800</v>
       </c>
       <c r="M17" s="3">
         <v>33800</v>
       </c>
       <c r="N17" s="3">
+        <v>33800</v>
+      </c>
+      <c r="O17" s="3">
         <v>34000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>32700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>38500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>28000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>25800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>23000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>18100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>53900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>13100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>15500</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-34700</v>
+      </c>
+      <c r="E18" s="3">
         <v>74200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-34300</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-34800</v>
       </c>
       <c r="G18" s="3">
         <v>-34800</v>
       </c>
       <c r="H18" s="3">
+        <v>-34800</v>
+      </c>
+      <c r="I18" s="3">
         <v>-31300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-30600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-31600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-30900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-32100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-33300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-31800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-31300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-37400</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1468,23 +1498,26 @@
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V18" s="3">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W18" s="3">
         <v>-13100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-15500</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1511,23 +1544,24 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-300</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
@@ -1538,26 +1572,26 @@
         <v>0</v>
       </c>
       <c r="K20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="L20" s="3">
         <v>200</v>
       </c>
       <c r="M20" s="3">
+        <v>200</v>
+      </c>
+      <c r="N20" s="3">
         <v>2100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>200</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1570,68 +1604,71 @@
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V20" s="3">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>200</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-31400</v>
+      </c>
+      <c r="E21" s="3">
         <v>77400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-30900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-31200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-31300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-28100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-27100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-28300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-27800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-29400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-28400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-27600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-29000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-36000</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1644,23 +1681,26 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W21" s="3">
         <v>-12600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-15000</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1679,17 +1719,17 @@
       <c r="H22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K22" s="3">
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3">
         <v>100</v>
-      </c>
-      <c r="L22" s="3">
-        <v>400</v>
       </c>
       <c r="M22" s="3">
         <v>400</v>
@@ -1698,7 +1738,7 @@
         <v>400</v>
       </c>
       <c r="O22" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="P22" s="3">
         <v>300</v>
@@ -1716,16 +1756,16 @@
         <v>300</v>
       </c>
       <c r="U22" s="3">
+        <v>300</v>
+      </c>
+      <c r="V22" s="3">
         <v>400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>100</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
-      </c>
-      <c r="X22" s="3" t="s">
-        <v>3</v>
+      <c r="X22" s="3">
+        <v>0</v>
       </c>
       <c r="Y22" s="3" t="s">
         <v>3</v>
@@ -1733,94 +1773,100 @@
       <c r="Z22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-32500</v>
+      </c>
+      <c r="E23" s="3">
         <v>76600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-34300</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-31200</v>
       </c>
       <c r="G23" s="3">
         <v>-31200</v>
       </c>
       <c r="H23" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="I23" s="3">
         <v>-28100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-40300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-32100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-32300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-30100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-31700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-30700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-31000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-37500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-28200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-26000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-23300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-18300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-53600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-13100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-15300</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3">
         <v>1800</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
         <v>0</v>
       </c>
@@ -1828,20 +1874,20 @@
         <v>0</v>
       </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>-900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1200</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
@@ -1854,8 +1900,8 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
+      <c r="R24" s="3">
+        <v>0</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>3</v>
@@ -1872,8 +1918,8 @@
       <c r="W24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
+      <c r="X24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y24" s="3">
         <v>0</v>
@@ -1881,8 +1927,11 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1955,156 +2004,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-32500</v>
+      </c>
+      <c r="E26" s="3">
         <v>76600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-36100</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-31200</v>
       </c>
       <c r="G26" s="3">
         <v>-31200</v>
       </c>
       <c r="H26" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="I26" s="3">
         <v>-28100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-39400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-32700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-33300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-31300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-31700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-30700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-31000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-37500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-28200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-26000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-23300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-18300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-53600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-13100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-15300</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-32500</v>
+      </c>
+      <c r="E27" s="3">
         <v>76600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-36100</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-31200</v>
       </c>
       <c r="G27" s="3">
         <v>-31200</v>
       </c>
       <c r="H27" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="I27" s="3">
         <v>-28100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-39400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-32700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-33300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-31300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-31700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-30700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-31000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-37500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-28200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-26000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-23300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-18300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-53600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-13100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-15300</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2177,8 +2235,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2251,8 +2312,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2325,8 +2389,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2399,23 +2466,26 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>300</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
@@ -2426,26 +2496,26 @@
         <v>0</v>
       </c>
       <c r="K32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="L32" s="3">
         <v>-200</v>
       </c>
       <c r="M32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N32" s="3">
         <v>-2100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-200</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2458,97 +2528,103 @@
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V32" s="3">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-200</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-32500</v>
+      </c>
+      <c r="E33" s="3">
         <v>76600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-36100</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-31200</v>
       </c>
       <c r="G33" s="3">
         <v>-31200</v>
       </c>
       <c r="H33" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="I33" s="3">
         <v>-28100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-39400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-32700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-33300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-31300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-31700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-30700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-31000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-37500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-28200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-26000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-23300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-18300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-53600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-13100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-15300</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2621,161 +2697,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-32500</v>
+      </c>
+      <c r="E35" s="3">
         <v>76600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-36100</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-31200</v>
       </c>
       <c r="G35" s="3">
         <v>-31200</v>
       </c>
       <c r="H35" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="I35" s="3">
         <v>-28100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-39400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-32700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-33300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-31300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-31700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-30700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-31000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-37500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-28200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-26000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-23300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-18300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-53600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-13100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-15300</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2802,8 +2887,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2830,65 +2916,66 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>56900</v>
+      </c>
+      <c r="E41" s="3">
         <v>51900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>58400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>52600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>41500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>46800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>47300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>55300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>64400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>86800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>84300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>111400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>112800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>126000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>56400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>101300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>272300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>79500</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2904,65 +2991,68 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>99000</v>
+      </c>
+      <c r="E42" s="3">
         <v>113300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>130900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>145500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>154900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>145200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>125400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>114200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>92000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>164600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>231200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>244500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>266000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>235000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>166400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>193900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>125300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>103500</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2978,41 +3068,44 @@
       <c r="Z42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>600</v>
+      </c>
+      <c r="E43" s="3">
         <v>1000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2200</v>
-      </c>
-      <c r="J43" s="3">
-        <v>1700</v>
       </c>
       <c r="K43" s="3">
         <v>1700</v>
       </c>
       <c r="L43" s="3">
+        <v>1700</v>
+      </c>
+      <c r="M43" s="3">
         <v>1500</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
       <c r="N43" s="3">
         <v>0</v>
       </c>
@@ -3052,8 +3145,11 @@
       <c r="Z43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3084,8 +3180,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3126,65 +3222,68 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3">
         <v>1700</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3">
         <v>1300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>5000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2400</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3200,65 +3299,68 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>160200</v>
+      </c>
+      <c r="E46" s="3">
         <v>169600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>194100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>206000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>203500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>199800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>177000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>173700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>161300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>255900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>319700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>361600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>383800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>365300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>228200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>300400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>402600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>185300</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3274,65 +3376,68 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E47" s="3">
         <v>20700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>30800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>46600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>73200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>57900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>89100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>114800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>144600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>83300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>51900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>39400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>50600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>105400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>135900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>105200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>42500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>63100</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3348,65 +3453,68 @@
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>84400</v>
+      </c>
+      <c r="E48" s="3">
         <v>87800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>90800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>94100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>98000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>88300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>92100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>106500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>108800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>114000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>111700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>107400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>94700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>76400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>69800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>60700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>46700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>33100</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3422,8 +3530,11 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3434,14 +3545,14 @@
         <v>34200</v>
       </c>
       <c r="F49" s="3">
+        <v>34200</v>
+      </c>
+      <c r="G49" s="3">
         <v>38500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>38400</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
       <c r="I49" s="3">
         <v>0</v>
       </c>
@@ -3454,11 +3565,11 @@
       <c r="L49" s="3">
         <v>0</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N49" s="3">
-        <v>0</v>
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O49" s="3">
         <v>0</v>
@@ -3496,8 +3607,11 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3570,8 +3684,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3644,25 +3761,28 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>3300</v>
+        <v>3200</v>
       </c>
       <c r="E52" s="3">
         <v>3300</v>
       </c>
       <c r="F52" s="3">
-        <v>3400</v>
+        <v>3300</v>
       </c>
       <c r="G52" s="3">
         <v>3400</v>
       </c>
       <c r="H52" s="3">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="I52" s="3">
         <v>2500</v>
@@ -3674,35 +3794,35 @@
         <v>2500</v>
       </c>
       <c r="L52" s="3">
+        <v>2500</v>
+      </c>
+      <c r="M52" s="3">
         <v>2900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3300</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>3500</v>
       </c>
       <c r="R52" s="3">
         <v>3500</v>
       </c>
       <c r="S52" s="3">
+        <v>3500</v>
+      </c>
+      <c r="T52" s="3">
         <v>3800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4500</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3718,8 +3838,11 @@
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3792,65 +3915,68 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>284700</v>
+      </c>
+      <c r="E54" s="3">
         <v>315600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>353200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>388600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>416400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>348500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>360700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>397600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>417200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>456200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>486500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>511800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>532600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>550300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>437400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>469700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>495600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>286100</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3866,8 +3992,11 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3894,8 +4023,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3922,65 +4052,66 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E57" s="3">
         <v>3600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2600</v>
-      </c>
-      <c r="G57" s="3">
-        <v>3400</v>
       </c>
       <c r="H57" s="3">
         <v>3400</v>
       </c>
       <c r="I57" s="3">
+        <v>3400</v>
+      </c>
+      <c r="J57" s="3">
         <v>2700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>9900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>7600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>11600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>13400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>8800</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3996,8 +4127,11 @@
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4008,44 +4142,44 @@
         <v>4900</v>
       </c>
       <c r="F58" s="3">
+        <v>4900</v>
+      </c>
+      <c r="G58" s="3">
         <v>3800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>10900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1600</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q58" s="3">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3">
         <v>1000</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4061,8 +4195,8 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
+      <c r="X58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y58" s="3">
         <v>0</v>
@@ -4070,65 +4204,68 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E59" s="3">
+      <c r="D59" s="3">
+        <v>0</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3">
         <v>109200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>17900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>17200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>15900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>12100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>7000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>8200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>7800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4100</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4144,65 +4281,68 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E60" s="3">
         <v>14500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>129800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>19800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>19200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>16100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>17800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>20400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>19200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>27700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>29800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>26900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>21600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>22000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>15700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>19900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>21200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>12900</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4218,65 +4358,68 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>46600</v>
+      </c>
+      <c r="E61" s="3">
         <v>47800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>49000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>50800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>52700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>44300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>46700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>45500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>40800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>41200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>8500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>10000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>8900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>9900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>9800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>9700</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4292,65 +4435,68 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E62" s="3">
         <v>8500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>8700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>9000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>9300</v>
       </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
       <c r="I62" s="3">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3">
         <v>100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>200</v>
-      </c>
-      <c r="K62" s="3">
-        <v>400</v>
       </c>
       <c r="L62" s="3">
         <v>400</v>
       </c>
       <c r="M62" s="3">
+        <v>400</v>
+      </c>
+      <c r="N62" s="3">
         <v>150300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>148500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>144600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>131700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>16600</v>
-      </c>
-      <c r="R62" s="3">
-        <v>17000</v>
       </c>
       <c r="S62" s="3">
         <v>17000</v>
       </c>
       <c r="T62" s="3">
+        <v>17000</v>
+      </c>
+      <c r="U62" s="3">
         <v>15600</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4366,8 +4512,11 @@
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4440,8 +4589,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4514,8 +4666,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4588,65 +4743,68 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>74800</v>
+      </c>
+      <c r="E66" s="3">
         <v>75200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>191900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>192900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>194300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>170600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>175900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>178300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>169600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>179100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>183800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>181500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>174600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>163600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>41100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>46700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>48000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>38200</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4662,8 +4820,11 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4690,8 +4851,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4764,8 +4926,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4838,8 +5003,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4892,11 +5060,11 @@
         <v>0</v>
       </c>
       <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
         <v>339400</v>
       </c>
-      <c r="U70" s="3">
-        <v>0</v>
-      </c>
       <c r="V70" s="3">
         <v>0</v>
       </c>
@@ -4912,8 +5080,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4986,65 +5157,68 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-738300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-705800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-782300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-746300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-715000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-683800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-655800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-616400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-583700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-550400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-519100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-487400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-456700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-425700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-388200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-360000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-334000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-310700</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5060,8 +5234,11 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5134,8 +5311,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5208,8 +5388,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5282,65 +5465,68 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>209900</v>
+      </c>
+      <c r="E76" s="3">
         <v>240400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>161400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>195700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>222100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>177900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>184800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>219200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>247600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>277200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>302700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>330200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>358000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>386700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>396200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>423000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>447600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-91600</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5356,8 +5542,11 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5430,161 +5619,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-32500</v>
+      </c>
+      <c r="E81" s="3">
         <v>76600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-36100</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-31200</v>
       </c>
       <c r="G81" s="3">
         <v>-31200</v>
       </c>
       <c r="H81" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="I81" s="3">
         <v>-28100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-39400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-32700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-33300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-31300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-31700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-30700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-31000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-37500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-28200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-26000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-23300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-18300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-53600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-13100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-15300</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5611,82 +5809,86 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E83" s="3">
         <v>3200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2900</v>
-      </c>
-      <c r="I83" s="3">
-        <v>2800</v>
       </c>
       <c r="J83" s="3">
         <v>2800</v>
       </c>
       <c r="K83" s="3">
+        <v>2800</v>
+      </c>
+      <c r="L83" s="3">
         <v>1700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1200</v>
-      </c>
-      <c r="M83" s="3">
-        <v>2800</v>
       </c>
       <c r="N83" s="3">
         <v>2800</v>
       </c>
       <c r="O83" s="3">
+        <v>2800</v>
+      </c>
+      <c r="P83" s="3">
         <v>1700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>300</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5759,8 +5961,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5833,8 +6038,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5907,8 +6115,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5981,8 +6192,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6055,82 +6269,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-27600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-34600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-24200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-28300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-27300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-30200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-26200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-13600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-19300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-29200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-22900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-24200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-25600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>86800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-24400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-24000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-18500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-22200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-41300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-9200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-11900</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6157,82 +6377,86 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-9800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-10500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-16700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-15700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-10600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-700</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6305,8 +6529,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6379,82 +6606,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>32500</v>
+      </c>
+      <c r="E94" s="3">
         <v>27900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>30600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>39200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-33900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>11500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>18600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>4200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>7000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>31300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>22700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>12500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-44000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-20600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-147100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-11600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-119000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-22800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>1700</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6481,8 +6714,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6513,8 +6747,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -6555,8 +6789,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6629,8 +6866,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6703,8 +6943,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6777,73 +7020,76 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>56700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>18200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-10100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>400</v>
-      </c>
-      <c r="M100" s="3">
-        <v>100</v>
       </c>
       <c r="N100" s="3">
         <v>100</v>
       </c>
       <c r="O100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>26900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>224600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>193500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>47700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>9600</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
+      <c r="X100" s="3">
+        <v>0</v>
       </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
@@ -6851,8 +7097,11 @@
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6883,8 +7132,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -6925,78 +7174,84 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-6600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>5800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>11100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-8000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-9100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-22400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-27100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-13000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>69600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-44800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-171500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>194500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>52300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-16300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-10200</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IPSC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IPSC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="92">
   <si>
     <t>IPSC</t>
   </si>
@@ -656,124 +656,127 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -783,48 +786,48 @@
       <c r="E8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3">
         <v>109200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4200</v>
-      </c>
-      <c r="H8" s="3">
-        <v>800</v>
       </c>
       <c r="I8" s="3">
         <v>800</v>
       </c>
       <c r="J8" s="3">
+        <v>800</v>
+      </c>
+      <c r="K8" s="3">
         <v>900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>300</v>
-      </c>
-      <c r="L8" s="3">
-        <v>100</v>
       </c>
       <c r="M8" s="3">
         <v>100</v>
       </c>
       <c r="N8" s="3">
+        <v>100</v>
+      </c>
+      <c r="O8" s="3">
         <v>1700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1100</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
@@ -837,8 +840,8 @@
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X8" s="3">
-        <v>0</v>
+      <c r="X8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y8" s="3">
         <v>0</v>
@@ -852,47 +855,50 @@
       <c r="AB8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E9" s="3">
         <v>22500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>26900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>26600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>29400</v>
-      </c>
-      <c r="H9" s="3">
-        <v>27200</v>
       </c>
       <c r="I9" s="3">
         <v>27200</v>
       </c>
       <c r="J9" s="3">
+        <v>27200</v>
+      </c>
+      <c r="K9" s="3">
         <v>23400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>22300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>22800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>22700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>24900</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
@@ -932,47 +938,50 @@
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-19700</v>
+      </c>
+      <c r="E10" s="3">
         <v>-22500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-26900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>82600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-25200</v>
-      </c>
-      <c r="H10" s="3">
-        <v>-26400</v>
       </c>
       <c r="I10" s="3">
         <v>-26400</v>
       </c>
       <c r="J10" s="3">
+        <v>-26400</v>
+      </c>
+      <c r="K10" s="3">
         <v>-22600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-22000</v>
-      </c>
-      <c r="L10" s="3">
-        <v>-22600</v>
       </c>
       <c r="M10" s="3">
         <v>-22600</v>
       </c>
       <c r="N10" s="3">
+        <v>-22600</v>
+      </c>
+      <c r="O10" s="3">
         <v>-23200</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1012,8 +1021,11 @@
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1042,88 +1054,92 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E12" s="3">
         <v>22500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>26900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>26600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>29400</v>
-      </c>
-      <c r="H12" s="3">
-        <v>27200</v>
       </c>
       <c r="I12" s="3">
         <v>27200</v>
       </c>
       <c r="J12" s="3">
+        <v>27200</v>
+      </c>
+      <c r="K12" s="3">
         <v>23400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>23300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>26800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>22700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>24900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>25600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>25900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>24500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>21200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>21800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>19500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>18900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>15400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>39700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>10800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>8500</v>
       </c>
-      <c r="Z12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1202,25 +1218,28 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E14" s="3">
         <v>6800</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
-        <v>3000</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
+        <v>4100</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
@@ -1228,20 +1247,20 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>13100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>4000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>4200</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1250,79 +1269,82 @@
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>10000</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W14" s="3">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X14" s="3">
         <v>4700</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>4700</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E15" s="3">
         <v>3100</v>
-      </c>
-      <c r="E15" s="3">
-        <v>3200</v>
       </c>
       <c r="F15" s="3">
         <v>3200</v>
       </c>
       <c r="G15" s="3">
-        <v>3300</v>
+        <v>3200</v>
       </c>
       <c r="H15" s="3">
         <v>3300</v>
       </c>
       <c r="I15" s="3">
+        <v>3300</v>
+      </c>
+      <c r="J15" s="3">
         <v>3500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>3400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>3200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2900</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1362,8 +1384,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1389,139 +1414,143 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>25600</v>
+      </c>
+      <c r="E17" s="3">
         <v>29400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>34700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>35000</v>
       </c>
-      <c r="G17" s="3">
-        <v>38500</v>
-      </c>
       <c r="H17" s="3">
+        <v>37400</v>
+      </c>
+      <c r="I17" s="3">
         <v>35600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>35500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>32200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>30900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>31800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>31000</v>
-      </c>
-      <c r="N17" s="3">
-        <v>33800</v>
       </c>
       <c r="O17" s="3">
         <v>33800</v>
       </c>
       <c r="P17" s="3">
+        <v>33800</v>
+      </c>
+      <c r="Q17" s="3">
         <v>34000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>32700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>38500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>28000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>25800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>23000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>18100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>53900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>13100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>15500</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-25600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-29400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-34700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>74200</v>
       </c>
-      <c r="G18" s="3">
-        <v>-34300</v>
-      </c>
       <c r="H18" s="3">
-        <v>-34800</v>
+        <v>-33200</v>
       </c>
       <c r="I18" s="3">
         <v>-34800</v>
       </c>
       <c r="J18" s="3">
+        <v>-34800</v>
+      </c>
+      <c r="K18" s="3">
         <v>-31300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-30600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-31600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-30900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-32100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-33300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-31800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-31300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-37400</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1534,23 +1563,26 @@
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X18" s="3">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y18" s="3">
         <v>-13100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-15500</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1579,8 +1611,9 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1591,17 +1624,17 @@
         <v>-100</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-300</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
@@ -1612,26 +1645,26 @@
         <v>0</v>
       </c>
       <c r="M20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="N20" s="3">
         <v>200</v>
       </c>
       <c r="O20" s="3">
+        <v>200</v>
+      </c>
+      <c r="P20" s="3">
         <v>2100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1644,74 +1677,77 @@
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X20" s="3">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y20" s="3">
         <v>100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>200</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-21900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-26100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-31400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>77400</v>
       </c>
-      <c r="G21" s="3">
-        <v>-30900</v>
-      </c>
       <c r="H21" s="3">
+        <v>-29800</v>
+      </c>
+      <c r="I21" s="3">
         <v>-31200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-31300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-28100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-27100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-28300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-27800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-29400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-28400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-27600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-29000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-36000</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1724,23 +1760,26 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y21" s="3">
         <v>-12600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-15000</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1765,17 +1804,17 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3">
         <v>100</v>
-      </c>
-      <c r="N22" s="3">
-        <v>400</v>
       </c>
       <c r="O22" s="3">
         <v>400</v>
@@ -1784,7 +1823,7 @@
         <v>400</v>
       </c>
       <c r="Q22" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="R22" s="3">
         <v>300</v>
@@ -1802,16 +1841,16 @@
         <v>300</v>
       </c>
       <c r="W22" s="3">
+        <v>300</v>
+      </c>
+      <c r="X22" s="3">
         <v>400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>100</v>
       </c>
-      <c r="Y22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="3" t="s">
-        <v>3</v>
+      <c r="Z22" s="3">
+        <v>0</v>
       </c>
       <c r="AA22" s="3" t="s">
         <v>3</v>
@@ -1819,93 +1858,99 @@
       <c r="AB22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-19200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-34400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-32500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>76600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-34300</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-31200</v>
       </c>
       <c r="I23" s="3">
         <v>-31200</v>
       </c>
       <c r="J23" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="K23" s="3">
         <v>-28100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-40300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-32100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-32300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-30100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-31700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-30700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-31000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-37500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-28200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-26000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-23300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-18300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-53600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-13100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-15300</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
+      <c r="D24" s="3">
+        <v>-100</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>3</v>
@@ -1913,12 +1958,12 @@
       <c r="F24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3">
         <v>1800</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
         <v>0</v>
       </c>
@@ -1926,20 +1971,20 @@
         <v>0</v>
       </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>-900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1200</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
         <v>0</v>
       </c>
@@ -1952,8 +1997,8 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
+      <c r="T24" s="3">
+        <v>0</v>
       </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
@@ -1970,8 +2015,8 @@
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA24" s="3">
         <v>0</v>
@@ -1979,8 +2024,11 @@
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2059,168 +2107,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-19200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-34400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-32500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>76600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-36100</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-31200</v>
       </c>
       <c r="I26" s="3">
         <v>-31200</v>
       </c>
       <c r="J26" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="K26" s="3">
         <v>-28100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-39400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-32700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-33300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-31300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-31700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-30700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-31000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-37500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-28200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-26000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-23300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-18300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-53600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-13100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-15300</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-19200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-34400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-32500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>76600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-36100</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-31200</v>
       </c>
       <c r="I27" s="3">
         <v>-31200</v>
       </c>
       <c r="J27" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="K27" s="3">
         <v>-28100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-39400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-32700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-33300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-31300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-31700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-30700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-31000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-37500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-28200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-26000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-23300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-18300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-53600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-13100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-15300</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2299,8 +2356,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2379,8 +2439,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2459,8 +2522,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2539,8 +2605,11 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2551,17 +2620,17 @@
         <v>100</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>300</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
@@ -2572,26 +2641,26 @@
         <v>0</v>
       </c>
       <c r="M32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="N32" s="3">
         <v>-200</v>
       </c>
       <c r="O32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="P32" s="3">
         <v>-2100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2604,103 +2673,109 @@
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X32" s="3">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-200</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-19200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-34400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-32500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>76600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-36100</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-31200</v>
       </c>
       <c r="I33" s="3">
         <v>-31200</v>
       </c>
       <c r="J33" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="K33" s="3">
         <v>-28100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-39400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-32700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-33300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-31300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-31700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-30700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-31000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-37500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-28200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-26000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-23300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-18300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-53600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-13100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-15300</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2779,173 +2854,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-19200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-34400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-32500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>76600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-36100</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-31200</v>
       </c>
       <c r="I35" s="3">
         <v>-31200</v>
       </c>
       <c r="J35" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="K35" s="3">
         <v>-28100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-39400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-32700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-33300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-31300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-31700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-30700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-31000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-37500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-28200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-26000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-23300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-18300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-53600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-13100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-15300</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2974,8 +3058,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3004,71 +3089,72 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>61900</v>
+      </c>
+      <c r="E41" s="3">
         <v>55500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>56900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>51900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>58400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>52600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>41500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>46800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>47300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>55300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>64400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>86800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>84300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>111400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>112800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>126000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>56400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>101300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>272300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>79500</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3084,71 +3170,74 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>55300</v>
+      </c>
+      <c r="E42" s="3">
         <v>77200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>99000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>113300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>130900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>145500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>154900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>145200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>125400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>114200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>92000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>164600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>231200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>244500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>266000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>235000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>166400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>193900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>125300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>103500</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3164,47 +3253,50 @@
       <c r="AB42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>700</v>
+      </c>
+      <c r="E43" s="3">
         <v>500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2200</v>
-      </c>
-      <c r="L43" s="3">
-        <v>1700</v>
       </c>
       <c r="M43" s="3">
         <v>1700</v>
       </c>
       <c r="N43" s="3">
+        <v>1700</v>
+      </c>
+      <c r="O43" s="3">
         <v>1500</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
       <c r="P43" s="3">
         <v>0</v>
       </c>
@@ -3244,8 +3336,11 @@
       <c r="AB43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3282,8 +3377,8 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3324,13 +3419,16 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3">
+        <v>1700</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>3</v>
@@ -3338,57 +3436,57 @@
       <c r="F45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3">
         <v>1700</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>1300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>5300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>5200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>5000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2400</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3404,71 +3502,74 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>120800</v>
+      </c>
+      <c r="E46" s="3">
         <v>137700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>160200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>169600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>194100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>206000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>203500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>199800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>177000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>173700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>161300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>255900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>319700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>361600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>383800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>365300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>228200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>300400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>402600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>185300</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3484,71 +3585,74 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3">
         <v>2700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>20700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>30800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>46600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>73200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>57900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>89100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>114800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>144600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>83300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>51900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>39400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>50600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>105400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>135900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>105200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>42500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>63100</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3564,71 +3668,74 @@
       <c r="AB47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>66200</v>
+      </c>
+      <c r="E48" s="3">
         <v>70300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>84400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>87800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>90800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>94100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>98000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>88300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>92100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>106500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>108800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>114000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>111700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>107400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>94700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>76400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>69800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>60700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>46700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>33100</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3644,8 +3751,11 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3662,14 +3772,14 @@
         <v>34200</v>
       </c>
       <c r="H49" s="3">
+        <v>34200</v>
+      </c>
+      <c r="I49" s="3">
         <v>38500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>38400</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
@@ -3682,11 +3792,11 @@
       <c r="N49" s="3">
         <v>0</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P49" s="3">
-        <v>0</v>
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q49" s="3">
         <v>0</v>
@@ -3724,8 +3834,11 @@
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3804,8 +3917,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3884,31 +4000,34 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E52" s="3">
         <v>2500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3200</v>
-      </c>
-      <c r="F52" s="3">
-        <v>3300</v>
       </c>
       <c r="G52" s="3">
         <v>3300</v>
       </c>
       <c r="H52" s="3">
-        <v>3400</v>
+        <v>3300</v>
       </c>
       <c r="I52" s="3">
         <v>3400</v>
       </c>
       <c r="J52" s="3">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="K52" s="3">
         <v>2500</v>
@@ -3920,35 +4039,35 @@
         <v>2500</v>
       </c>
       <c r="N52" s="3">
+        <v>2500</v>
+      </c>
+      <c r="O52" s="3">
         <v>2900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3300</v>
-      </c>
-      <c r="S52" s="3">
-        <v>3500</v>
       </c>
       <c r="T52" s="3">
         <v>3500</v>
       </c>
       <c r="U52" s="3">
+        <v>3500</v>
+      </c>
+      <c r="V52" s="3">
         <v>3800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4500</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3964,8 +4083,11 @@
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4044,71 +4166,74 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>223700</v>
+      </c>
+      <c r="E54" s="3">
         <v>244700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>284700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>315600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>353200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>388600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>416400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>348500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>360700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>397600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>417200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>456200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>486500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>511800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>532600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>550300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>437400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>469700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>495600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>286100</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4124,8 +4249,11 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4154,8 +4282,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4184,71 +4313,72 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E57" s="3">
         <v>2600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2600</v>
-      </c>
-      <c r="I57" s="3">
-        <v>3400</v>
       </c>
       <c r="J57" s="3">
         <v>3400</v>
       </c>
       <c r="K57" s="3">
+        <v>3400</v>
+      </c>
+      <c r="L57" s="3">
         <v>2700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>9900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>7600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>11600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>13400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>8800</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4264,16 +4394,19 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E58" s="3">
         <v>3800</v>
-      </c>
-      <c r="E58" s="3">
-        <v>4900</v>
       </c>
       <c r="F58" s="3">
         <v>4900</v>
@@ -4282,44 +4415,44 @@
         <v>4900</v>
       </c>
       <c r="H58" s="3">
+        <v>4900</v>
+      </c>
+      <c r="I58" s="3">
         <v>3800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>10900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>6500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1600</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S58" s="3">
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T58" s="3">
         <v>1000</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4335,8 +4468,8 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z58" s="3">
-        <v>0</v>
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA58" s="3">
         <v>0</v>
@@ -4344,71 +4477,74 @@
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E59" s="3">
         <v>8400</v>
       </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="F59" s="3">
+        <v>0</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3">
         <v>109200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>17900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>17200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>15900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>12100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>7000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>8200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>7800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4100</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4424,71 +4560,74 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E60" s="3">
         <v>22000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>14900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>14500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>129800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>19800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>19200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>16100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>17800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>20400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>19200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>27700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>29800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>26900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>21600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>22000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>15700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>19900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>21200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>12900</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4504,71 +4643,74 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>40200</v>
+      </c>
+      <c r="E61" s="3">
         <v>41200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>46600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>47800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>49000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>50800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>52700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>44300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>46700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>45500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>40800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>41200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>8500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>10000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>8900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>9900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>9800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>9700</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4584,71 +4726,74 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3">
         <v>800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>8900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>8500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>8700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>9000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>9300</v>
       </c>
-      <c r="J62" s="3">
-        <v>0</v>
-      </c>
       <c r="K62" s="3">
+        <v>0</v>
+      </c>
+      <c r="L62" s="3">
         <v>100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>200</v>
-      </c>
-      <c r="M62" s="3">
-        <v>400</v>
       </c>
       <c r="N62" s="3">
         <v>400</v>
       </c>
       <c r="O62" s="3">
+        <v>400</v>
+      </c>
+      <c r="P62" s="3">
         <v>150300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>148500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>144600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>131700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>16600</v>
-      </c>
-      <c r="T62" s="3">
-        <v>17000</v>
       </c>
       <c r="U62" s="3">
         <v>17000</v>
       </c>
       <c r="V62" s="3">
+        <v>17000</v>
+      </c>
+      <c r="W62" s="3">
         <v>15600</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4664,8 +4809,11 @@
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4744,8 +4892,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4824,8 +4975,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4904,71 +5058,74 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>64800</v>
+      </c>
+      <c r="E66" s="3">
         <v>68400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>74800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>75200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>191900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>192900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>194300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>170600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>175900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>178300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>169600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>179100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>183800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>181500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>174600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>163600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>41100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>46700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>48000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>38200</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4984,8 +5141,11 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5014,8 +5174,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5094,8 +5255,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5174,8 +5338,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5234,11 +5401,11 @@
         <v>0</v>
       </c>
       <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
         <v>339400</v>
       </c>
-      <c r="W70" s="3">
-        <v>0</v>
-      </c>
       <c r="X70" s="3">
         <v>0</v>
       </c>
@@ -5254,8 +5421,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5334,71 +5504,74 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-791900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-772700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-738300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-705800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-782300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-746300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-715000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-683800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-655800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-616400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-583700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-550400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-519100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-487400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-456700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-425700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-388200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-360000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-334000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-310700</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5414,8 +5587,11 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5494,8 +5670,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5574,8 +5753,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5654,71 +5836,74 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>158900</v>
+      </c>
+      <c r="E76" s="3">
         <v>176300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>209900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>240400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>161400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>195700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>222100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>177900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>184800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>219200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>247600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>277200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>302700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>330200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>358000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>386700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>396200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>423000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>447600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-91600</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5734,8 +5919,11 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5814,173 +6002,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-19200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-34400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-32500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>76600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-36100</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-31200</v>
       </c>
       <c r="I81" s="3">
         <v>-31200</v>
       </c>
       <c r="J81" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="K81" s="3">
         <v>-28100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-39400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-32700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-33300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-31300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-31700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-30700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-31000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-37500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-28200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-26000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-23300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-18300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-53600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-13100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-15300</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6009,8 +6206,9 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6018,79 +6216,82 @@
         <v>3300</v>
       </c>
       <c r="E83" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F83" s="3">
         <v>3500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2900</v>
-      </c>
-      <c r="K83" s="3">
-        <v>2800</v>
       </c>
       <c r="L83" s="3">
         <v>2800</v>
       </c>
       <c r="M83" s="3">
+        <v>2800</v>
+      </c>
+      <c r="N83" s="3">
         <v>1700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1200</v>
-      </c>
-      <c r="O83" s="3">
-        <v>2800</v>
       </c>
       <c r="P83" s="3">
         <v>2800</v>
       </c>
       <c r="Q83" s="3">
+        <v>2800</v>
+      </c>
+      <c r="R83" s="3">
         <v>1700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>300</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6169,8 +6370,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6249,8 +6453,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6329,8 +6536,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6409,8 +6619,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6489,88 +6702,94 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-25600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-27600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-34600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-24200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-28300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-27300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-30200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-26200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-13600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-19300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-29200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-22900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-24200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-25600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>86800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-24400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-24000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-18500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-22200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-41300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-9200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-11900</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6599,88 +6818,92 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-6300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-10500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-16700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-15700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-10600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-4700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-700</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6759,8 +6982,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6839,88 +7065,94 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E94" s="3">
         <v>24700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>32500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>27900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>30600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>39200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-33900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>11500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>18600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>4200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>7000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>31300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>22700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>12500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-44000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-20600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-147100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-11600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-119000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-22800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>1700</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6949,8 +7181,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6987,8 +7220,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -7029,8 +7262,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7109,8 +7345,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7189,8 +7428,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7269,79 +7511,82 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E100" s="3">
         <v>0</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>56700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>18200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-10100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>400</v>
-      </c>
-      <c r="O100" s="3">
-        <v>100</v>
       </c>
       <c r="P100" s="3">
         <v>100</v>
       </c>
       <c r="Q100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>26900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>224600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>193500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>47700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>9600</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z100" s="3" t="s">
-        <v>3</v>
+      <c r="Z100" s="3">
+        <v>0</v>
       </c>
       <c r="AA100" s="3" t="s">
         <v>3</v>
@@ -7349,8 +7594,11 @@
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7387,8 +7635,8 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -7429,84 +7677,90 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>4900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-6600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>5800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>11100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-8000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-9100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-22400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-27100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-13000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>69600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-44800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-171500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>194500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>52300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-16300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-10200</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IPSC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IPSC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="92">
   <si>
     <t>IPSC</t>
   </si>
@@ -656,181 +656,185 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>3</v>
+      <c r="E8" s="3">
+        <v>0</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3">
         <v>109200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4200</v>
-      </c>
-      <c r="I8" s="3">
-        <v>800</v>
       </c>
       <c r="J8" s="3">
         <v>800</v>
       </c>
       <c r="K8" s="3">
+        <v>800</v>
+      </c>
+      <c r="L8" s="3">
         <v>900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>300</v>
-      </c>
-      <c r="M8" s="3">
-        <v>100</v>
       </c>
       <c r="N8" s="3">
         <v>100</v>
       </c>
       <c r="O8" s="3">
+        <v>100</v>
+      </c>
+      <c r="P8" s="3">
         <v>1700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1100</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
@@ -843,8 +847,8 @@
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y8" s="3">
-        <v>0</v>
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z8" s="3">
         <v>0</v>
@@ -858,50 +862,53 @@
       <c r="AC8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E9" s="3">
         <v>19700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>22500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>26900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>26600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>29400</v>
-      </c>
-      <c r="I9" s="3">
-        <v>27200</v>
       </c>
       <c r="J9" s="3">
         <v>27200</v>
       </c>
       <c r="K9" s="3">
+        <v>27200</v>
+      </c>
+      <c r="L9" s="3">
         <v>23400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>22300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>22800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>22700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>24900</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
@@ -941,50 +948,53 @@
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-17100</v>
+      </c>
+      <c r="E10" s="3">
         <v>-19700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-22500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-26900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>82600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-25200</v>
-      </c>
-      <c r="I10" s="3">
-        <v>-26400</v>
       </c>
       <c r="J10" s="3">
         <v>-26400</v>
       </c>
       <c r="K10" s="3">
+        <v>-26400</v>
+      </c>
+      <c r="L10" s="3">
         <v>-22600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-22000</v>
-      </c>
-      <c r="M10" s="3">
-        <v>-22600</v>
       </c>
       <c r="N10" s="3">
         <v>-22600</v>
       </c>
       <c r="O10" s="3">
+        <v>-22600</v>
+      </c>
+      <c r="P10" s="3">
         <v>-23200</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1024,8 +1034,11 @@
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1055,91 +1068,95 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E12" s="3">
         <v>19700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>22500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>26900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>26600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>29400</v>
-      </c>
-      <c r="I12" s="3">
-        <v>27200</v>
       </c>
       <c r="J12" s="3">
         <v>27200</v>
       </c>
       <c r="K12" s="3">
+        <v>27200</v>
+      </c>
+      <c r="L12" s="3">
         <v>23400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>23300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>26800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>22700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>24900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>25600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>25900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>24500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>21200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>21800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>19500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>18900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>15400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>39700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>10800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>8500</v>
       </c>
-      <c r="AA12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1221,49 +1238,52 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E14" s="3">
         <v>-4900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>6800</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H14" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I14" s="3">
         <v>4100</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>13100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>4000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>4200</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1272,82 +1292,85 @@
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>10000</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y14" s="3">
         <v>4700</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>4700</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E15" s="3">
         <v>3600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>3100</v>
-      </c>
-      <c r="F15" s="3">
-        <v>3200</v>
       </c>
       <c r="G15" s="3">
         <v>3200</v>
       </c>
       <c r="H15" s="3">
-        <v>3300</v>
+        <v>3200</v>
       </c>
       <c r="I15" s="3">
         <v>3300</v>
       </c>
       <c r="J15" s="3">
+        <v>3300</v>
+      </c>
+      <c r="K15" s="3">
         <v>3500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>3600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>3400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>3200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2900</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1387,8 +1410,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1415,145 +1441,149 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>25500</v>
+      </c>
+      <c r="E17" s="3">
         <v>25600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>29400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>34700</v>
       </c>
-      <c r="G17" s="3">
-        <v>35000</v>
-      </c>
       <c r="H17" s="3">
+        <v>35200</v>
+      </c>
+      <c r="I17" s="3">
         <v>37400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>35600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>35500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>32200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>30900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>31800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>31000</v>
-      </c>
-      <c r="O17" s="3">
-        <v>33800</v>
       </c>
       <c r="P17" s="3">
         <v>33800</v>
       </c>
       <c r="Q17" s="3">
+        <v>33800</v>
+      </c>
+      <c r="R17" s="3">
         <v>34000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>32700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>38500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>28000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>25800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>23000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>18100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>53900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>13100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>15500</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-25500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-25600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-29400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-34700</v>
       </c>
-      <c r="G18" s="3">
-        <v>74200</v>
-      </c>
       <c r="H18" s="3">
+        <v>73900</v>
+      </c>
+      <c r="I18" s="3">
         <v>-33200</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-34800</v>
       </c>
       <c r="J18" s="3">
         <v>-34800</v>
       </c>
       <c r="K18" s="3">
+        <v>-34800</v>
+      </c>
+      <c r="L18" s="3">
         <v>-31300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-30600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-31600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-30900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-32100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-33300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-31800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-31300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-37400</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1566,23 +1596,26 @@
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z18" s="3">
         <v>-13100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-15500</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1612,13 +1645,14 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
         <v>-100</v>
@@ -1627,17 +1661,17 @@
         <v>-100</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-300</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
@@ -1648,26 +1682,26 @@
         <v>0</v>
       </c>
       <c r="N20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="O20" s="3">
         <v>200</v>
       </c>
       <c r="P20" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q20" s="3">
         <v>2100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>200</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1680,77 +1714,80 @@
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z20" s="3">
         <v>100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>200</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-22500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-21900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-26100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-31400</v>
       </c>
-      <c r="G21" s="3">
-        <v>77400</v>
-      </c>
       <c r="H21" s="3">
+        <v>77100</v>
+      </c>
+      <c r="I21" s="3">
         <v>-29800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-31200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-31300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-28100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-27100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-28300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-27800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-29400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-28400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-27600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-29000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-36000</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1763,23 +1800,26 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z21" s="3">
         <v>-12600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-15000</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1807,17 +1847,17 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="3">
         <v>100</v>
-      </c>
-      <c r="O22" s="3">
-        <v>400</v>
       </c>
       <c r="P22" s="3">
         <v>400</v>
@@ -1826,7 +1866,7 @@
         <v>400</v>
       </c>
       <c r="R22" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="S22" s="3">
         <v>300</v>
@@ -1844,16 +1884,16 @@
         <v>300</v>
       </c>
       <c r="X22" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y22" s="3">
         <v>400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>100</v>
       </c>
-      <c r="Z22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="3" t="s">
-        <v>3</v>
+      <c r="AA22" s="3">
+        <v>0</v>
       </c>
       <c r="AB22" s="3" t="s">
         <v>3</v>
@@ -1861,112 +1901,118 @@
       <c r="AC22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-21600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-19200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-34400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-32500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>76600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-34300</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-31200</v>
       </c>
       <c r="J23" s="3">
         <v>-31200</v>
       </c>
       <c r="K23" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="L23" s="3">
         <v>-28100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-40300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-32100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-32300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-30100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-31700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-30700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-31000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-37500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-28200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-26000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-23300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-18300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-53600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-13100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-15300</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3">
         <v>-100</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H24" s="3">
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3">
         <v>1800</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
         <v>0</v>
       </c>
@@ -1974,20 +2020,20 @@
         <v>0</v>
       </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>-900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1200</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
@@ -2000,8 +2046,8 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
+      <c r="U24" s="3">
+        <v>0</v>
       </c>
       <c r="V24" s="3" t="s">
         <v>3</v>
@@ -2018,8 +2064,8 @@
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
+      <c r="AA24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB24" s="3">
         <v>0</v>
@@ -2027,8 +2073,11 @@
       <c r="AC24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2110,174 +2159,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-21600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-19200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-34400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-32500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>76600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-36100</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-31200</v>
       </c>
       <c r="J26" s="3">
         <v>-31200</v>
       </c>
       <c r="K26" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="L26" s="3">
         <v>-28100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-39400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-32700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-33300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-31300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-31700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-30700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-31000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-37500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-28200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-26000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-23300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-18300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-53600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-13100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-15300</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-21600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-19200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-34400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-32500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>76600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-36100</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-31200</v>
       </c>
       <c r="J27" s="3">
         <v>-31200</v>
       </c>
       <c r="K27" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="L27" s="3">
         <v>-28100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-39400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-32700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-33300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-31300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-31700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-30700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-31000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-37500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-28200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-26000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-23300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-18300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-53600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-13100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-15300</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2359,8 +2417,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2442,8 +2503,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2525,8 +2589,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2608,13 +2675,16 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
         <v>100</v>
@@ -2623,17 +2693,17 @@
         <v>100</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>300</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
@@ -2644,26 +2714,26 @@
         <v>0</v>
       </c>
       <c r="N32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="O32" s="3">
         <v>-200</v>
       </c>
       <c r="P32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-200</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2676,106 +2746,112 @@
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-200</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-21600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-19200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-34400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-32500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>76600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-36100</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-31200</v>
       </c>
       <c r="J33" s="3">
         <v>-31200</v>
       </c>
       <c r="K33" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="L33" s="3">
         <v>-28100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-39400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-32700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-33300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-31300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-31700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-30700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-31000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-37500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-28200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-26000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-23300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-18300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-53600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-13100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-15300</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2857,179 +2933,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-21600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-19200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-34400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-32500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>76600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-36100</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-31200</v>
       </c>
       <c r="J35" s="3">
         <v>-31200</v>
       </c>
       <c r="K35" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="L35" s="3">
         <v>-28100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-39400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-32700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-33300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-31300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-31700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-30700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-31000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-37500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-28200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-26000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-23300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-18300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-53600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-13100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-15300</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3059,8 +3144,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3090,74 +3176,75 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>51000</v>
+      </c>
+      <c r="E41" s="3">
         <v>61900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>55500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>56900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>51900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>58400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>52600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>41500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>46800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>47300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>55300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>64400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>86800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>84300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>111400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>112800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>126000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>56400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>101300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>272300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>79500</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3173,74 +3260,77 @@
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>83800</v>
+      </c>
+      <c r="E42" s="3">
         <v>55300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>77200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>99000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>113300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>130900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>145500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>154900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>145200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>125400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>114200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>92000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>164600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>231200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>244500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>266000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>235000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>166400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>193900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>125300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>103500</v>
       </c>
-      <c r="X42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3256,50 +3346,53 @@
       <c r="AC42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E43" s="3">
         <v>700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2200</v>
-      </c>
-      <c r="M43" s="3">
-        <v>1700</v>
       </c>
       <c r="N43" s="3">
         <v>1700</v>
       </c>
       <c r="O43" s="3">
+        <v>1700</v>
+      </c>
+      <c r="P43" s="3">
         <v>1500</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
       <c r="Q43" s="3">
         <v>0</v>
       </c>
@@ -3339,8 +3432,11 @@
       <c r="AC43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3380,8 +3476,8 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3422,74 +3518,77 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3">
         <v>1700</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3">
         <v>1700</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>1300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>5300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>5200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>5000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2400</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3505,74 +3604,77 @@
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>139000</v>
+      </c>
+      <c r="E46" s="3">
         <v>120800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>137700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>160200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>169600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>194100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>206000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>203500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>199800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>177000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>173700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>161300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>255900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>319700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>361600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>383800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>365300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>228200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>300400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>402600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>185300</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3588,74 +3690,77 @@
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>3</v>
+      <c r="D47" s="3">
+        <v>82200</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3">
         <v>2700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>20700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>30800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>46600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>73200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>57900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>89100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>114800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>144600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>83300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>51900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>39400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>50600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>105400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>135900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>105200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>42500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>63100</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3671,74 +3776,77 @@
       <c r="AC47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>68600</v>
+      </c>
+      <c r="E48" s="3">
         <v>66200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>70300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>84400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>87800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>90800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>94100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>98000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>88300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>92100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>106500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>108800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>114000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>111700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>107400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>94700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>76400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>69800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>60700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>46700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>33100</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3754,8 +3862,11 @@
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3775,14 +3886,14 @@
         <v>34200</v>
       </c>
       <c r="I49" s="3">
+        <v>34200</v>
+      </c>
+      <c r="J49" s="3">
         <v>38500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>38400</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
       <c r="L49" s="3">
         <v>0</v>
       </c>
@@ -3795,11 +3906,11 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>0</v>
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R49" s="3">
         <v>0</v>
@@ -3837,8 +3948,11 @@
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3920,8 +4034,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4003,8 +4120,11 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4012,25 +4132,25 @@
         <v>2600</v>
       </c>
       <c r="E52" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F52" s="3">
         <v>2500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3200</v>
-      </c>
-      <c r="G52" s="3">
-        <v>3300</v>
       </c>
       <c r="H52" s="3">
         <v>3300</v>
       </c>
       <c r="I52" s="3">
-        <v>3400</v>
+        <v>3300</v>
       </c>
       <c r="J52" s="3">
         <v>3400</v>
       </c>
       <c r="K52" s="3">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="L52" s="3">
         <v>2500</v>
@@ -4042,35 +4162,35 @@
         <v>2500</v>
       </c>
       <c r="O52" s="3">
+        <v>2500</v>
+      </c>
+      <c r="P52" s="3">
         <v>2900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3300</v>
-      </c>
-      <c r="T52" s="3">
-        <v>3500</v>
       </c>
       <c r="U52" s="3">
         <v>3500</v>
       </c>
       <c r="V52" s="3">
+        <v>3500</v>
+      </c>
+      <c r="W52" s="3">
         <v>3800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4500</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4086,8 +4206,11 @@
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4169,74 +4292,77 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>326600</v>
+      </c>
+      <c r="E54" s="3">
         <v>223700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>244700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>284700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>315600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>353200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>388600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>416400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>348500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>360700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>397600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>417200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>456200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>486500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>511800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>532600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>550300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>437400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>469700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>495600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>286100</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4252,8 +4378,11 @@
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4283,8 +4412,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4314,74 +4444,75 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E57" s="3">
         <v>4800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2600</v>
-      </c>
-      <c r="J57" s="3">
-        <v>3400</v>
       </c>
       <c r="K57" s="3">
         <v>3400</v>
       </c>
       <c r="L57" s="3">
+        <v>3400</v>
+      </c>
+      <c r="M57" s="3">
         <v>2700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>9900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>7600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>11600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>13400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>8800</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4397,19 +4528,22 @@
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E58" s="3">
         <v>3300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3800</v>
-      </c>
-      <c r="F58" s="3">
-        <v>4900</v>
       </c>
       <c r="G58" s="3">
         <v>4900</v>
@@ -4418,44 +4552,44 @@
         <v>4900</v>
       </c>
       <c r="I58" s="3">
+        <v>4900</v>
+      </c>
+      <c r="J58" s="3">
         <v>3800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>10900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>6500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>4000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1600</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T58" s="3">
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U58" s="3">
         <v>1000</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4471,8 +4605,8 @@
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA58" s="3">
-        <v>0</v>
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB58" s="3">
         <v>0</v>
@@ -4480,74 +4614,77 @@
       <c r="AC58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E59" s="3">
         <v>3800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>8400</v>
       </c>
-      <c r="F59" s="3">
-        <v>0</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="G59" s="3">
+        <v>0</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3">
         <v>109200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>17900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>17200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>15900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>12100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>7000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>8200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>7800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4100</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4563,74 +4700,77 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E60" s="3">
         <v>20200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>22000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>14900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>14500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>129800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>19800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>19200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>16100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>17800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>20400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>19200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>27700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>29800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>26900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>21600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>22000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>15700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>19900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>21200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>12900</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4646,74 +4786,77 @@
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>43900</v>
+      </c>
+      <c r="E61" s="3">
         <v>40200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>41200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>46600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>47800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>49000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>50800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>52700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>44300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>46700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>45500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>40800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>41200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>6100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>8500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>10000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>8900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>9900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>9800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>9700</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4729,74 +4872,77 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E62" s="3">
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3">
         <v>800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>8900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>8500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>8700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>9000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>9300</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
+        <v>0</v>
+      </c>
+      <c r="M62" s="3">
         <v>100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>200</v>
-      </c>
-      <c r="N62" s="3">
-        <v>400</v>
       </c>
       <c r="O62" s="3">
         <v>400</v>
       </c>
       <c r="P62" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q62" s="3">
         <v>150300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>148500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>144600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>131700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>16600</v>
-      </c>
-      <c r="U62" s="3">
-        <v>17000</v>
       </c>
       <c r="V62" s="3">
         <v>17000</v>
       </c>
       <c r="W62" s="3">
+        <v>17000</v>
+      </c>
+      <c r="X62" s="3">
         <v>15600</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4812,8 +4958,11 @@
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4895,8 +5044,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4978,8 +5130,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5061,74 +5216,77 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>61800</v>
+      </c>
+      <c r="E66" s="3">
         <v>64800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>68400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>74800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>75200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>191900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>192900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>194300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>170600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>175900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>178300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>169600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>179100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>183800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>181500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>174600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>163600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>41100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>46700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>48000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>38200</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5144,8 +5302,11 @@
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5175,8 +5336,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5258,8 +5420,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5341,8 +5506,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5404,11 +5572,11 @@
         <v>0</v>
       </c>
       <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
         <v>339400</v>
       </c>
-      <c r="X70" s="3">
-        <v>0</v>
-      </c>
       <c r="Y70" s="3">
         <v>0</v>
       </c>
@@ -5424,8 +5592,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5507,74 +5678,77 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-813600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-791900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-772700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-738300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-705800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-782300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-746300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-715000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-683800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-655800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-616400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-583700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-550400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-519100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-487400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-456700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-425700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-388200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-360000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-334000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-310700</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5590,8 +5764,11 @@
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5673,8 +5850,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5756,8 +5936,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5839,74 +6022,77 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>264700</v>
+      </c>
+      <c r="E76" s="3">
         <v>158900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>176300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>209900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>240400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>161400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>195700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>222100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>177900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>184800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>219200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>247600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>277200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>302700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>330200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>358000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>386700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>396200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>423000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>447600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-91600</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5922,8 +6108,11 @@
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6005,179 +6194,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-21600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-19200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-34400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-32500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>76600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-36100</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-31200</v>
       </c>
       <c r="J81" s="3">
         <v>-31200</v>
       </c>
       <c r="K81" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="L81" s="3">
         <v>-28100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-39400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-32700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-33300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-31300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-31700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-30700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-31000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-37500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-28200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-26000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-23300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-18300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-53600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-13100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-15300</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6207,91 +6405,95 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>3300</v>
+        <v>3200</v>
       </c>
       <c r="E83" s="3">
         <v>3300</v>
       </c>
       <c r="F83" s="3">
+        <v>3300</v>
+      </c>
+      <c r="G83" s="3">
         <v>3500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2900</v>
-      </c>
-      <c r="L83" s="3">
-        <v>2800</v>
       </c>
       <c r="M83" s="3">
         <v>2800</v>
       </c>
       <c r="N83" s="3">
+        <v>2800</v>
+      </c>
+      <c r="O83" s="3">
         <v>1700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1200</v>
-      </c>
-      <c r="P83" s="3">
-        <v>2800</v>
       </c>
       <c r="Q83" s="3">
         <v>2800</v>
       </c>
       <c r="R83" s="3">
+        <v>2800</v>
+      </c>
+      <c r="S83" s="3">
         <v>1700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>300</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6373,8 +6575,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6456,8 +6661,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6539,8 +6747,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6622,8 +6833,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6705,91 +6919,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-25300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-16100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-25600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-27600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-34600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-24200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-28300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-27300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-30200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-26200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-13600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-19300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-29200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-22900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-24200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-25600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>86800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-24400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-24000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-18500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-22200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-41300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-9200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-11900</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6819,91 +7039,95 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E91" s="3">
         <v>100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-9800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-10500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-16700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-15700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-10600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-4700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-700</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6985,8 +7209,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7068,91 +7295,97 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-112600</v>
+      </c>
+      <c r="E94" s="3">
         <v>22400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>24700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>32500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>27900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>30600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>39200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-33900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>11500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>18600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>4200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>7000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>31300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>22700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>12500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-44000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-20600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-147100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-11600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-119000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-22800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>1700</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7182,8 +7415,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7223,8 +7457,8 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7265,8 +7499,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7348,8 +7585,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7431,8 +7671,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7514,82 +7757,85 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>126600</v>
+      </c>
+      <c r="E100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>56700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>18200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-10100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>400</v>
-      </c>
-      <c r="P100" s="3">
-        <v>100</v>
       </c>
       <c r="Q100" s="3">
         <v>100</v>
       </c>
       <c r="R100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>26900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>224600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>193500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>47700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>9600</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA100" s="3" t="s">
-        <v>3</v>
+      <c r="AA100" s="3">
+        <v>0</v>
       </c>
       <c r="AB100" s="3" t="s">
         <v>3</v>
@@ -7597,8 +7843,11 @@
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7638,8 +7887,8 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -7680,87 +7929,93 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="E102" s="3">
         <v>6300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>4900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-6600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>5800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>11100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-8000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-9100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-22400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-27100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-13000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>69600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-44800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-171500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>194500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>52300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-16300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-10200</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AC102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
